--- a/Bird Species Database.xlsx
+++ b/Bird Species Database.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5876" uniqueCount="4265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5876" uniqueCount="4264">
   <si>
     <t>Alphabetical Name</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Scientific Name</t>
   </si>
   <si>
-    <t>Family Name</t>
+    <t>Group Name</t>
   </si>
   <si>
     <t>Albatross, Amsterdam</t>
@@ -8477,9 +8477,6 @@
   </si>
   <si>
     <t>Yellowlegs</t>
-  </si>
-  <si>
-    <t>Group Name</t>
   </si>
   <si>
     <t>Accentor, Alpine</t>
@@ -25540,54 +25537,54 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2821</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
+        <v>2821</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>2822</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>2823</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>2824</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>2825</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>2826</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>2827</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>2828</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>2829</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>2830</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>2831</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>2832</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>64</v>
@@ -25601,35 +25598,35 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
+        <v>2833</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>2834</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>2835</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>2836</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>2837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>2838</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>2839</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>2840</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>106</v>
@@ -25643,7 +25640,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>110</v>
@@ -25657,7 +25654,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>148</v>
@@ -25671,7 +25668,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>151</v>
@@ -25685,30 +25682,30 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>2845</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>2846</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>2847</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>2848</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>2849</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>2850</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>2851</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="14">
@@ -25727,49 +25724,49 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>2852</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>2853</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>2854</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>2855</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>2855</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>2856</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>2856</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>2857</v>
-      </c>
       <c r="D16" s="5" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>2857</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>2858</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>2858</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>2859</v>
-      </c>
       <c r="D17" s="5" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>163</v>
@@ -25783,69 +25780,69 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>2860</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>2861</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>2861</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>2862</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
+        <v>2862</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>2862</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>2863</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>2863</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>2864</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>2864</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>2865</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>2865</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>2866</v>
-      </c>
       <c r="D21" s="5" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>2867</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>2868</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>2869</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>2870</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>2871</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>2872</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>2873</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>202</v>
@@ -25853,13 +25850,13 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>2874</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>2875</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>2876</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>202</v>
@@ -25867,13 +25864,13 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>2877</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>2878</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>2879</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>202</v>
@@ -25881,13 +25878,13 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>2880</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>2881</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>2882</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>202</v>
@@ -25895,13 +25892,13 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>2883</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>2884</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>2885</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>202</v>
@@ -25909,13 +25906,13 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
+        <v>2885</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>2886</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>2887</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>2888</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>202</v>
@@ -25923,13 +25920,13 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>2889</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>2890</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>2891</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>202</v>
@@ -25937,13 +25934,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
+        <v>2891</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>2892</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>2893</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>2894</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>202</v>
@@ -25951,13 +25948,13 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>2895</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>2896</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>2897</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>202</v>
@@ -25965,13 +25962,13 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
+        <v>2897</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>2898</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>2899</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>2900</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>202</v>
@@ -25993,13 +25990,13 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>2901</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>2902</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>2903</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>202</v>
@@ -26007,13 +26004,13 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>2904</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>2905</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>2906</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>202</v>
@@ -26021,13 +26018,13 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>2907</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>2908</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>2909</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>202</v>
@@ -26035,13 +26032,13 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
+        <v>2909</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>2910</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>2911</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>2912</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>202</v>
@@ -26049,13 +26046,13 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>2913</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>2914</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>2915</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>202</v>
@@ -26063,13 +26060,13 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
+        <v>2915</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>2916</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>2917</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>2918</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>202</v>
@@ -26077,13 +26074,13 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>2919</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>2920</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>2921</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>202</v>
@@ -26091,13 +26088,13 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>2922</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>2923</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>2924</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>202</v>
@@ -26105,13 +26102,13 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>2925</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>2926</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>2927</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>234</v>
@@ -26119,13 +26116,13 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
+        <v>2927</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>2928</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>2929</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>2930</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>234</v>
@@ -26133,10 +26130,10 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>2931</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2932</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>256</v>
@@ -26147,13 +26144,13 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>2933</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>2934</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>2935</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>257</v>
@@ -26161,41 +26158,41 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2935</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>2936</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>2936</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>2937</v>
-      </c>
       <c r="D46" s="5" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>2938</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2939</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>677</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>2941</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>2942</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>2943</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>315</v>
@@ -26203,10 +26200,10 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B49" s="5" t="s">
         <v>2944</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2945</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>314</v>
@@ -26217,49 +26214,49 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
+        <v>2945</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>2946</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>2947</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>2948</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>2949</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
+        <v>2949</v>
+      </c>
+      <c r="B51" s="5" t="s">
         <v>2950</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>2951</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>2952</v>
-      </c>
       <c r="D51" s="5" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>2954</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>2955</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>2956</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>388</v>
@@ -26273,27 +26270,27 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
+        <v>2957</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>2958</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>2959</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>2960</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>2961</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
+        <v>2961</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>2962</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>2963</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>2964</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>393</v>
@@ -26301,10 +26298,10 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>2965</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2966</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>406</v>
@@ -26315,13 +26312,13 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>2967</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>2968</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>2969</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>397</v>
@@ -26329,13 +26326,13 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>2970</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>2971</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>2972</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>423</v>
@@ -26343,24 +26340,24 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>2973</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>2974</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>2975</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>2976</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>2977</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2978</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>442</v>
@@ -26371,7 +26368,7 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>447</v>
@@ -26399,7 +26396,7 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>453</v>
@@ -26413,13 +26410,13 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
+        <v>2980</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>2981</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>2982</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>2983</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>461</v>
@@ -26427,13 +26424,13 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>2984</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>2985</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>2986</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>461</v>
@@ -26441,13 +26438,13 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
+        <v>2986</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>2987</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>2988</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>2989</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>461</v>
@@ -26455,55 +26452,55 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
+        <v>2989</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>2990</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>2991</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>2992</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>2993</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
+        <v>2993</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>2994</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>2995</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>2996</v>
-      </c>
       <c r="D68" s="5" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>2997</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>2998</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>2999</v>
-      </c>
       <c r="D69" s="5" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
+        <v>2999</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>3000</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>3001</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>3002</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>479</v>
@@ -26511,13 +26508,13 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>3003</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="5" t="s">
         <v>3004</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>3005</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>479</v>
@@ -26525,7 +26522,7 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>481</v>
@@ -26539,7 +26536,7 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>484</v>
@@ -26553,7 +26550,7 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>500</v>
@@ -26567,7 +26564,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>506</v>
@@ -26581,13 +26578,13 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
+        <v>3009</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>3010</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="C76" s="5" t="s">
         <v>3011</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>3012</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>489</v>
@@ -26595,7 +26592,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>540</v>
@@ -26609,13 +26606,13 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>3014</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="C78" s="5" t="s">
         <v>3015</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>3016</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>542</v>
@@ -26623,13 +26620,13 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>3017</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="C79" s="5" t="s">
         <v>3018</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>3019</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>542</v>
@@ -26637,41 +26634,41 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
+        <v>3019</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>3020</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="C80" s="5" t="s">
         <v>3021</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="D80" s="5" t="s">
         <v>3022</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>3023</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
+        <v>3023</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>3024</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>3025</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="D81" s="5" t="s">
         <v>3026</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>3027</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>3028</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>3029</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>3030</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>550</v>
@@ -26679,13 +26676,13 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>3031</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="C83" s="5" t="s">
         <v>3032</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>3033</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>550</v>
@@ -26693,27 +26690,27 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
+        <v>3033</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>3033</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>3034</v>
       </c>
-      <c r="B84" s="5" t="s">
-        <v>3034</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>3035</v>
-      </c>
       <c r="D84" s="5" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>3036</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="C85" s="5" t="s">
         <v>3037</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>3038</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>584</v>
@@ -26721,13 +26718,13 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>3039</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>3040</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>3041</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>595</v>
@@ -26735,13 +26732,13 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>3042</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="C87" s="5" t="s">
         <v>3043</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>3044</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>595</v>
@@ -26749,13 +26746,13 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B88" s="5" t="s">
         <v>3045</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>3046</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>3047</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>595</v>
@@ -26763,13 +26760,13 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
+        <v>3047</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>3048</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>3049</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>3050</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>595</v>
@@ -26777,13 +26774,13 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
+        <v>3050</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>3051</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>3052</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>3053</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>595</v>
@@ -26791,13 +26788,13 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B91" s="5" t="s">
         <v>3054</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>3055</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>3056</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>595</v>
@@ -26805,13 +26802,13 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B92" s="5" t="s">
         <v>3057</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>3058</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>3059</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>595</v>
@@ -26819,13 +26816,13 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B93" s="5" t="s">
         <v>3060</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="C93" s="5" t="s">
         <v>3061</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>3062</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>595</v>
@@ -26833,13 +26830,13 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B94" s="5" t="s">
         <v>3063</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="C94" s="5" t="s">
         <v>3064</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>3065</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>595</v>
@@ -26847,13 +26844,13 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B95" s="5" t="s">
         <v>3066</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="C95" s="5" t="s">
         <v>3067</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>3068</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>595</v>
@@ -26861,13 +26858,13 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B96" s="5" t="s">
         <v>3069</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="C96" s="5" t="s">
         <v>3070</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>3071</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>595</v>
@@ -26889,41 +26886,41 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
+        <v>3071</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>3071</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>3072</v>
       </c>
-      <c r="B98" s="5" t="s">
-        <v>3072</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>3073</v>
-      </c>
       <c r="D98" s="5" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>3074</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="C99" s="5" t="s">
         <v>3075</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="D99" s="5" t="s">
         <v>3076</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>3077</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>3078</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="C100" s="5" t="s">
         <v>3079</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>3080</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>619</v>
@@ -26931,7 +26928,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>630</v>
@@ -26945,13 +26942,13 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>3082</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="C102" s="5" t="s">
         <v>3083</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>3084</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>619</v>
@@ -26959,13 +26956,13 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>3085</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="C103" s="5" t="s">
         <v>3086</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>3087</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>619</v>
@@ -26973,13 +26970,13 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
+        <v>3087</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>3088</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="C104" s="5" t="s">
         <v>3089</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>3090</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>619</v>
@@ -26987,7 +26984,7 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>639</v>
@@ -27001,13 +26998,13 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>3092</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="C106" s="5" t="s">
         <v>3093</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>3094</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>619</v>
@@ -27015,7 +27012,7 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>651</v>
@@ -27029,13 +27026,13 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B108" s="5" t="s">
         <v>3096</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="C108" s="5" t="s">
         <v>3097</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>3098</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>619</v>
@@ -27043,7 +27040,7 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>663</v>
@@ -27057,7 +27054,7 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>667</v>
@@ -27085,66 +27082,66 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>3101</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="C112" s="5" t="s">
         <v>3102</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="D112" s="5" t="s">
         <v>3103</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>3104</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>3105</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="C113" s="5" t="s">
         <v>3106</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>3107</v>
-      </c>
       <c r="D113" s="5" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>3108</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="C114" s="5" t="s">
         <v>3109</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>3110</v>
-      </c>
       <c r="D114" s="5" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
+        <v>3110</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>3111</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="C115" s="5" t="s">
         <v>3112</v>
       </c>
-      <c r="C115" s="5" t="s">
-        <v>3113</v>
-      </c>
       <c r="D115" s="5" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
+        <v>3113</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>3114</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>3115</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>700</v>
@@ -27155,7 +27152,7 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>705</v>
@@ -27169,7 +27166,7 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>711</v>
@@ -27183,13 +27180,13 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
+        <v>3117</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>3118</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="C119" s="5" t="s">
         <v>3119</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>3120</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>697</v>
@@ -27197,27 +27194,27 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>3120</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>3121</v>
       </c>
-      <c r="B120" s="5" t="s">
-        <v>3121</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>3122</v>
-      </c>
       <c r="D120" s="5" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>3123</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="C121" s="5" t="s">
         <v>3124</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>3125</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>729</v>
@@ -27225,13 +27222,13 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
+        <v>3125</v>
+      </c>
+      <c r="B122" s="5" t="s">
         <v>3126</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="C122" s="5" t="s">
         <v>3127</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>3128</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>729</v>
@@ -27239,13 +27236,13 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>3129</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="C123" s="5" t="s">
         <v>3130</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>3131</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>729</v>
@@ -27253,41 +27250,41 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
+        <v>3131</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>3132</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="C124" s="5" t="s">
         <v>3133</v>
       </c>
-      <c r="C124" s="5" t="s">
+      <c r="D124" s="5" t="s">
         <v>3134</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>3135</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>3136</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="C125" s="5" t="s">
         <v>3137</v>
       </c>
-      <c r="C125" s="5" t="s">
+      <c r="D125" s="5" t="s">
         <v>3138</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>3139</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B126" s="5" t="s">
         <v>3140</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="C126" s="5" t="s">
         <v>3141</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>3142</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>757</v>
@@ -27295,13 +27292,13 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
+        <v>3142</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>3143</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="C127" s="5" t="s">
         <v>3144</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>3145</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>757</v>
@@ -27309,7 +27306,7 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>755</v>
@@ -27323,7 +27320,7 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>797</v>
@@ -27337,13 +27334,13 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
+        <v>3147</v>
+      </c>
+      <c r="B130" s="5" t="s">
         <v>3148</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="C130" s="5" t="s">
         <v>3149</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>3150</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>780</v>
@@ -27365,13 +27362,13 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>3151</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="C132" s="5" t="s">
         <v>3152</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>3153</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>780</v>
@@ -27379,13 +27376,13 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
+        <v>3153</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>3154</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="C133" s="5" t="s">
         <v>3155</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>3156</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>780</v>
@@ -27393,7 +27390,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>824</v>
@@ -27407,13 +27404,13 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
+        <v>3157</v>
+      </c>
+      <c r="B135" s="5" t="s">
         <v>3158</v>
       </c>
-      <c r="B135" s="5" t="s">
+      <c r="C135" s="5" t="s">
         <v>3159</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>3160</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>858</v>
@@ -27421,24 +27418,24 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>3160</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>3161</v>
       </c>
-      <c r="B136" s="5" t="s">
-        <v>3161</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>3162</v>
-      </c>
       <c r="D136" s="5" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>3163</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>3164</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>865</v>
@@ -27449,13 +27446,13 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>3165</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="C138" s="5" t="s">
         <v>3166</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>3167</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>869</v>
@@ -27477,7 +27474,7 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>880</v>
@@ -27491,7 +27488,7 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>884</v>
@@ -27505,111 +27502,111 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>3170</v>
       </c>
-      <c r="B142" s="5" t="s">
-        <v>3170</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>3171</v>
-      </c>
       <c r="D142" s="5" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
+        <v>3171</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>3172</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>3173</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>1723</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B144" s="5" t="s">
         <v>3175</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="C144" s="5" t="s">
         <v>3176</v>
       </c>
-      <c r="C144" s="5" t="s">
-        <v>3177</v>
-      </c>
       <c r="D144" s="5" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
+        <v>3177</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>3178</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>3179</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>1751</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
+        <v>3179</v>
+      </c>
+      <c r="B146" s="5" t="s">
         <v>3180</v>
       </c>
-      <c r="B146" s="5" t="s">
+      <c r="C146" s="5" t="s">
         <v>3181</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="D146" s="5" t="s">
         <v>3182</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>3183</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
+        <v>3183</v>
+      </c>
+      <c r="B147" s="5" t="s">
         <v>3184</v>
       </c>
-      <c r="B147" s="5" t="s">
+      <c r="C147" s="5" t="s">
         <v>3185</v>
       </c>
-      <c r="C147" s="5" t="s">
-        <v>3186</v>
-      </c>
       <c r="D147" s="5" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="s">
+        <v>3186</v>
+      </c>
+      <c r="B148" s="5" t="s">
         <v>3187</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="C148" s="5" t="s">
         <v>3188</v>
       </c>
-      <c r="C148" s="5" t="s">
+      <c r="D148" s="5" t="s">
         <v>3189</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>3190</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="s">
+        <v>3190</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>3191</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="C149" s="5" t="s">
         <v>3192</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>3193</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>892</v>
@@ -27617,13 +27614,13 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>3194</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="C150" s="5" t="s">
         <v>3195</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>3196</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>892</v>
@@ -27631,13 +27628,13 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>3197</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="C151" s="5" t="s">
         <v>3198</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>3199</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>892</v>
@@ -27645,13 +27642,13 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="s">
+        <v>3199</v>
+      </c>
+      <c r="B152" s="5" t="s">
         <v>3200</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="C152" s="5" t="s">
         <v>3201</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>3202</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>892</v>
@@ -27659,7 +27656,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>894</v>
@@ -27673,13 +27670,13 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="s">
+        <v>3203</v>
+      </c>
+      <c r="B154" s="5" t="s">
         <v>3204</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="C154" s="5" t="s">
         <v>3205</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>3206</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>892</v>
@@ -27687,13 +27684,13 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="s">
+        <v>3206</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>3207</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="C155" s="5" t="s">
         <v>3208</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>3209</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>892</v>
@@ -27701,13 +27698,13 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="s">
+        <v>3209</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>3210</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="C156" s="5" t="s">
         <v>3211</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>3212</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>892</v>
@@ -27715,13 +27712,13 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>3213</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="C157" s="5" t="s">
         <v>3214</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>3215</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>892</v>
@@ -27729,13 +27726,13 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="s">
+        <v>3215</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>3216</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="C158" s="5" t="s">
         <v>3217</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>3218</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>892</v>
@@ -27743,13 +27740,13 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>3219</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="C159" s="5" t="s">
         <v>3220</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>3221</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>892</v>
@@ -27757,13 +27754,13 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="s">
+        <v>3221</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>3222</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="C160" s="5" t="s">
         <v>3223</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>3224</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>892</v>
@@ -27771,13 +27768,13 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>3225</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="C161" s="5" t="s">
         <v>3226</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>3227</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>902</v>
@@ -27785,24 +27782,24 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B162" s="5" t="s">
         <v>3228</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="C162" s="5" t="s">
         <v>3229</v>
       </c>
-      <c r="C162" s="5" t="s">
+      <c r="D162" s="5" t="s">
         <v>3230</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>3231</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>3232</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>3233</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>918</v>
@@ -27813,7 +27810,7 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>921</v>
@@ -27827,13 +27824,13 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B165" s="5" t="s">
         <v>3235</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="C165" s="5" t="s">
         <v>3236</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>3237</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>919</v>
@@ -27841,7 +27838,7 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>924</v>
@@ -27855,13 +27852,13 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B167" s="5" t="s">
         <v>3239</v>
       </c>
-      <c r="B167" s="5" t="s">
+      <c r="C167" s="5" t="s">
         <v>3240</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>3241</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>919</v>
@@ -27869,13 +27866,13 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="s">
+        <v>3241</v>
+      </c>
+      <c r="B168" s="5" t="s">
         <v>3242</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="C168" s="5" t="s">
         <v>3243</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>3244</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>919</v>
@@ -27883,21 +27880,21 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>3245</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="C169" s="5" t="s">
         <v>3246</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="D169" s="5" t="s">
         <v>3247</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>3248</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>937</v>
@@ -27911,83 +27908,83 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B171" s="5" t="s">
         <v>3250</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="C171" s="5" t="s">
         <v>3251</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="D171" s="5" t="s">
         <v>3252</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>3253</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B172" s="5" t="s">
         <v>3254</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>3255</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>2554</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B173" s="5" t="s">
         <v>3256</v>
       </c>
-      <c r="B173" s="5" t="s">
+      <c r="C173" s="5" t="s">
         <v>3257</v>
       </c>
-      <c r="C173" s="5" t="s">
+      <c r="D173" s="5" t="s">
         <v>3258</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>3259</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B174" s="5" t="s">
         <v>3260</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="C174" s="5" t="s">
         <v>3261</v>
       </c>
-      <c r="C174" s="5" t="s">
+      <c r="D174" s="5" t="s">
         <v>3262</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>3263</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>3264</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="C175" s="5" t="s">
         <v>3265</v>
       </c>
-      <c r="C175" s="5" t="s">
+      <c r="D175" s="5" t="s">
         <v>3266</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>3267</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B176" s="5" t="s">
         <v>3268</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="C176" s="5" t="s">
         <v>3269</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>3270</v>
       </c>
       <c r="D176" s="5" t="s">
         <v>950</v>
@@ -27995,13 +27992,13 @@
     </row>
     <row r="177">
       <c r="A177" s="5" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B177" s="5" t="s">
         <v>3271</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="C177" s="5" t="s">
         <v>3272</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>3273</v>
       </c>
       <c r="D177" s="5" t="s">
         <v>950</v>
@@ -28009,10 +28006,10 @@
     </row>
     <row r="178">
       <c r="A178" s="5" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B178" s="5" t="s">
         <v>3274</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>3275</v>
       </c>
       <c r="C178" s="5" t="s">
         <v>949</v>
@@ -28023,13 +28020,13 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>3276</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="C179" s="5" t="s">
         <v>3277</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>3278</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>950</v>
@@ -28037,13 +28034,13 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B180" s="5" t="s">
         <v>3279</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="C180" s="5" t="s">
         <v>3280</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>3281</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>950</v>
@@ -28051,13 +28048,13 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>3282</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="C181" s="5" t="s">
         <v>3283</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>3284</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>950</v>
@@ -28065,13 +28062,13 @@
     </row>
     <row r="182">
       <c r="A182" s="5" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B182" s="5" t="s">
         <v>3285</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="C182" s="5" t="s">
         <v>3286</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>3287</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>950</v>
@@ -28079,10 +28076,10 @@
     </row>
     <row r="183">
       <c r="A183" s="5" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B183" s="5" t="s">
         <v>3288</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>3289</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>953</v>
@@ -28093,13 +28090,13 @@
     </row>
     <row r="184">
       <c r="A184" s="5" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B184" s="5" t="s">
         <v>3290</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="C184" s="5" t="s">
         <v>3291</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>3292</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>950</v>
@@ -28107,13 +28104,13 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>3293</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="C185" s="5" t="s">
         <v>3294</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>3295</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>950</v>
@@ -28121,13 +28118,13 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B186" s="5" t="s">
         <v>3296</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="C186" s="5" t="s">
         <v>3297</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>3298</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>950</v>
@@ -28135,13 +28132,13 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>3299</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="C187" s="5" t="s">
         <v>3300</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>3301</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>950</v>
@@ -28163,7 +28160,7 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>967</v>
@@ -28177,13 +28174,13 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B190" s="5" t="s">
         <v>3303</v>
       </c>
-      <c r="B190" s="5" t="s">
+      <c r="C190" s="5" t="s">
         <v>3304</v>
-      </c>
-      <c r="C190" s="5" t="s">
-        <v>3305</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>950</v>
@@ -28191,13 +28188,13 @@
     </row>
     <row r="191">
       <c r="A191" s="5" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B191" s="5" t="s">
         <v>3306</v>
       </c>
-      <c r="B191" s="5" t="s">
+      <c r="C191" s="5" t="s">
         <v>3307</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>3308</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>950</v>
@@ -28205,13 +28202,13 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B192" s="5" t="s">
         <v>3309</v>
       </c>
-      <c r="B192" s="5" t="s">
+      <c r="C192" s="5" t="s">
         <v>3310</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>3311</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>950</v>
@@ -28219,13 +28216,13 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B193" s="5" t="s">
         <v>3312</v>
       </c>
-      <c r="B193" s="5" t="s">
+      <c r="C193" s="5" t="s">
         <v>3313</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>3314</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>950</v>
@@ -28233,13 +28230,13 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="s">
+        <v>3314</v>
+      </c>
+      <c r="B194" s="5" t="s">
         <v>3315</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="C194" s="5" t="s">
         <v>3316</v>
-      </c>
-      <c r="C194" s="5" t="s">
-        <v>3317</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>950</v>
@@ -28247,10 +28244,10 @@
     </row>
     <row r="195">
       <c r="A195" s="5" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B195" s="5" t="s">
         <v>3318</v>
-      </c>
-      <c r="B195" s="5" t="s">
-        <v>3319</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>971</v>
@@ -28261,7 +28258,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>973</v>
@@ -28275,13 +28272,13 @@
     </row>
     <row r="197">
       <c r="A197" s="5" t="s">
+        <v>3320</v>
+      </c>
+      <c r="B197" s="5" t="s">
         <v>3321</v>
       </c>
-      <c r="B197" s="5" t="s">
+      <c r="C197" s="5" t="s">
         <v>3322</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>3323</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>950</v>
@@ -28289,27 +28286,27 @@
     </row>
     <row r="198">
       <c r="A198" s="5" t="s">
+        <v>3323</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>3323</v>
+      </c>
+      <c r="C198" s="5" t="s">
         <v>3324</v>
       </c>
-      <c r="B198" s="5" t="s">
-        <v>3324</v>
-      </c>
-      <c r="C198" s="5" t="s">
-        <v>3325</v>
-      </c>
       <c r="D198" s="5" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="s">
+        <v>3325</v>
+      </c>
+      <c r="B199" s="5" t="s">
         <v>3326</v>
       </c>
-      <c r="B199" s="5" t="s">
+      <c r="C199" s="5" t="s">
         <v>3327</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>3328</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>983</v>
@@ -28317,10 +28314,10 @@
     </row>
     <row r="200">
       <c r="A200" s="5" t="s">
+        <v>3328</v>
+      </c>
+      <c r="B200" s="5" t="s">
         <v>3329</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>3330</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>989</v>
@@ -28331,13 +28328,13 @@
     </row>
     <row r="201">
       <c r="A201" s="5" t="s">
+        <v>3330</v>
+      </c>
+      <c r="B201" s="5" t="s">
         <v>3331</v>
       </c>
-      <c r="B201" s="5" t="s">
+      <c r="C201" s="5" t="s">
         <v>3332</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>3333</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>983</v>
@@ -28345,7 +28342,7 @@
     </row>
     <row r="202">
       <c r="A202" s="5" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>991</v>
@@ -28373,27 +28370,27 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>3334</v>
+      </c>
+      <c r="C204" s="5" t="s">
         <v>3335</v>
       </c>
-      <c r="B204" s="5" t="s">
-        <v>3335</v>
-      </c>
-      <c r="C204" s="5" t="s">
-        <v>3336</v>
-      </c>
       <c r="D204" s="5" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="s">
+        <v>3336</v>
+      </c>
+      <c r="B205" s="5" t="s">
         <v>3337</v>
       </c>
-      <c r="B205" s="5" t="s">
+      <c r="C205" s="5" t="s">
         <v>3338</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>3339</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>999</v>
@@ -28401,7 +28398,7 @@
     </row>
     <row r="206">
       <c r="A206" s="5" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>1021</v>
@@ -28415,10 +28412,10 @@
     </row>
     <row r="207">
       <c r="A207" s="5" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B207" s="5" t="s">
         <v>3341</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>3342</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>1031</v>
@@ -28429,13 +28426,13 @@
     </row>
     <row r="208">
       <c r="A208" s="5" t="s">
+        <v>3342</v>
+      </c>
+      <c r="B208" s="5" t="s">
         <v>3343</v>
       </c>
-      <c r="B208" s="5" t="s">
+      <c r="C208" s="5" t="s">
         <v>3344</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>3345</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>1019</v>
@@ -28443,7 +28440,7 @@
     </row>
     <row r="209">
       <c r="A209" s="5" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>1042</v>
@@ -28457,7 +28454,7 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>1048</v>
@@ -28471,13 +28468,13 @@
     </row>
     <row r="211">
       <c r="A211" s="5" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B211" s="5" t="s">
         <v>3348</v>
       </c>
-      <c r="B211" s="5" t="s">
+      <c r="C211" s="5" t="s">
         <v>3349</v>
-      </c>
-      <c r="C211" s="5" t="s">
-        <v>3350</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>1019</v>
@@ -28485,13 +28482,13 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B212" s="5" t="s">
         <v>3351</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="C212" s="5" t="s">
         <v>3352</v>
-      </c>
-      <c r="C212" s="5" t="s">
-        <v>3353</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>1019</v>
@@ -28499,7 +28496,7 @@
     </row>
     <row r="213">
       <c r="A213" s="5" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>1058</v>
@@ -28513,24 +28510,24 @@
     </row>
     <row r="214">
       <c r="A214" s="5" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B214" s="5" t="s">
         <v>3355</v>
-      </c>
-      <c r="B214" s="5" t="s">
-        <v>3356</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>263</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="s">
+        <v>3357</v>
+      </c>
+      <c r="B215" s="5" t="s">
         <v>3358</v>
-      </c>
-      <c r="B215" s="5" t="s">
-        <v>3359</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>1076</v>
@@ -28541,35 +28538,35 @@
     </row>
     <row r="216">
       <c r="A216" s="5" t="s">
+        <v>3359</v>
+      </c>
+      <c r="B216" s="5" t="s">
         <v>3360</v>
       </c>
-      <c r="B216" s="5" t="s">
+      <c r="C216" s="5" t="s">
         <v>3361</v>
       </c>
-      <c r="C216" s="5" t="s">
+      <c r="D216" s="5" t="s">
         <v>3362</v>
-      </c>
-      <c r="D216" s="5" t="s">
-        <v>3363</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="s">
+        <v>3363</v>
+      </c>
+      <c r="B217" s="5" t="s">
         <v>3364</v>
-      </c>
-      <c r="B217" s="5" t="s">
-        <v>3365</v>
       </c>
       <c r="C217" s="5" t="s">
         <v>1378</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>1102</v>
@@ -28583,7 +28580,7 @@
     </row>
     <row r="219">
       <c r="A219" s="5" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>1106</v>
@@ -28597,13 +28594,13 @@
     </row>
     <row r="220">
       <c r="A220" s="5" t="s">
+        <v>3368</v>
+      </c>
+      <c r="B220" s="5" t="s">
         <v>3369</v>
       </c>
-      <c r="B220" s="5" t="s">
+      <c r="C220" s="5" t="s">
         <v>3370</v>
-      </c>
-      <c r="C220" s="5" t="s">
-        <v>3371</v>
       </c>
       <c r="D220" s="5" t="s">
         <v>1104</v>
@@ -28611,35 +28608,35 @@
     </row>
     <row r="221">
       <c r="A221" s="5" t="s">
+        <v>3371</v>
+      </c>
+      <c r="B221" s="5" t="s">
         <v>3372</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="C221" s="5" t="s">
         <v>3373</v>
       </c>
-      <c r="C221" s="5" t="s">
+      <c r="D221" s="5" t="s">
         <v>3374</v>
-      </c>
-      <c r="D221" s="5" t="s">
-        <v>3375</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B222" s="5" t="s">
         <v>3376</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="C222" s="5" t="s">
         <v>3377</v>
       </c>
-      <c r="C222" s="5" t="s">
-        <v>3378</v>
-      </c>
       <c r="D222" s="5" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>1132</v>
@@ -28653,7 +28650,7 @@
     </row>
     <row r="224">
       <c r="A224" s="5" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>1136</v>
@@ -28667,7 +28664,7 @@
     </row>
     <row r="225">
       <c r="A225" s="5" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>1139</v>
@@ -28681,41 +28678,41 @@
     </row>
     <row r="226">
       <c r="A226" s="5" t="s">
+        <v>3381</v>
+      </c>
+      <c r="B226" s="5" t="s">
         <v>3382</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="C226" s="5" t="s">
         <v>3383</v>
       </c>
-      <c r="C226" s="5" t="s">
+      <c r="D226" s="5" t="s">
         <v>3384</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>3385</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B227" s="5" t="s">
         <v>3386</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="C227" s="5" t="s">
         <v>3387</v>
       </c>
-      <c r="C227" s="5" t="s">
+      <c r="D227" s="5" t="s">
         <v>3388</v>
-      </c>
-      <c r="D227" s="5" t="s">
-        <v>3389</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="s">
+        <v>3389</v>
+      </c>
+      <c r="B228" s="5" t="s">
         <v>3390</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="C228" s="5" t="s">
         <v>3391</v>
-      </c>
-      <c r="C228" s="5" t="s">
-        <v>3392</v>
       </c>
       <c r="D228" s="5" t="s">
         <v>1144</v>
@@ -28723,13 +28720,13 @@
     </row>
     <row r="229">
       <c r="A229" s="5" t="s">
+        <v>3392</v>
+      </c>
+      <c r="B229" s="5" t="s">
         <v>3393</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="C229" s="5" t="s">
         <v>3394</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>3395</v>
       </c>
       <c r="D229" s="5" t="s">
         <v>1144</v>
@@ -28737,7 +28734,7 @@
     </row>
     <row r="230">
       <c r="A230" s="5" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>1149</v>
@@ -28751,27 +28748,27 @@
     </row>
     <row r="231">
       <c r="A231" s="5" t="s">
+        <v>3396</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>3396</v>
+      </c>
+      <c r="C231" s="5" t="s">
         <v>3397</v>
       </c>
-      <c r="B231" s="5" t="s">
-        <v>3397</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>3398</v>
-      </c>
       <c r="D231" s="5" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="5" t="s">
+        <v>3398</v>
+      </c>
+      <c r="B232" s="5" t="s">
         <v>3399</v>
       </c>
-      <c r="B232" s="5" t="s">
+      <c r="C232" s="5" t="s">
         <v>3400</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>3401</v>
       </c>
       <c r="D232" s="5" t="s">
         <v>1157</v>
@@ -28779,13 +28776,13 @@
     </row>
     <row r="233">
       <c r="A233" s="5" t="s">
+        <v>3401</v>
+      </c>
+      <c r="B233" s="5" t="s">
         <v>3402</v>
       </c>
-      <c r="B233" s="5" t="s">
+      <c r="C233" s="5" t="s">
         <v>3403</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>3404</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>1157</v>
@@ -28793,7 +28790,7 @@
     </row>
     <row r="234">
       <c r="A234" s="5" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>1186</v>
@@ -28821,13 +28818,13 @@
     </row>
     <row r="236">
       <c r="A236" s="5" t="s">
+        <v>3405</v>
+      </c>
+      <c r="B236" s="5" t="s">
         <v>3406</v>
       </c>
-      <c r="B236" s="5" t="s">
+      <c r="C236" s="5" t="s">
         <v>3407</v>
-      </c>
-      <c r="C236" s="5" t="s">
-        <v>3408</v>
       </c>
       <c r="D236" s="5" t="s">
         <v>1188</v>
@@ -28835,7 +28832,7 @@
     </row>
     <row r="237">
       <c r="A237" s="5" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>1193</v>
@@ -28849,7 +28846,7 @@
     </row>
     <row r="238">
       <c r="A238" s="5" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>1197</v>
@@ -28863,7 +28860,7 @@
     </row>
     <row r="239">
       <c r="A239" s="5" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>1201</v>
@@ -28877,13 +28874,13 @@
     </row>
     <row r="240">
       <c r="A240" s="5" t="s">
+        <v>3411</v>
+      </c>
+      <c r="B240" s="5" t="s">
         <v>3412</v>
       </c>
-      <c r="B240" s="5" t="s">
+      <c r="C240" s="5" t="s">
         <v>3413</v>
-      </c>
-      <c r="C240" s="5" t="s">
-        <v>3414</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>1226</v>
@@ -28891,13 +28888,13 @@
     </row>
     <row r="241">
       <c r="A241" s="5" t="s">
+        <v>3414</v>
+      </c>
+      <c r="B241" s="5" t="s">
         <v>3415</v>
       </c>
-      <c r="B241" s="5" t="s">
+      <c r="C241" s="5" t="s">
         <v>3416</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>3417</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>1226</v>
@@ -28905,13 +28902,13 @@
     </row>
     <row r="242">
       <c r="A242" s="5" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B242" s="5" t="s">
         <v>3418</v>
       </c>
-      <c r="B242" s="5" t="s">
+      <c r="C242" s="5" t="s">
         <v>3419</v>
-      </c>
-      <c r="C242" s="5" t="s">
-        <v>3420</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>1226</v>
@@ -28919,13 +28916,13 @@
     </row>
     <row r="243">
       <c r="A243" s="5" t="s">
+        <v>3420</v>
+      </c>
+      <c r="B243" s="5" t="s">
         <v>3421</v>
       </c>
-      <c r="B243" s="5" t="s">
+      <c r="C243" s="5" t="s">
         <v>3422</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>3423</v>
       </c>
       <c r="D243" s="5" t="s">
         <v>1226</v>
@@ -28939,7 +28936,7 @@
         <v>1243</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>1226</v>
@@ -28947,13 +28944,13 @@
     </row>
     <row r="245">
       <c r="A245" s="5" t="s">
+        <v>3424</v>
+      </c>
+      <c r="B245" s="5" t="s">
         <v>3425</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="C245" s="5" t="s">
         <v>3426</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>3427</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>1226</v>
@@ -28961,13 +28958,13 @@
     </row>
     <row r="246">
       <c r="A246" s="5" t="s">
+        <v>3427</v>
+      </c>
+      <c r="B246" s="5" t="s">
         <v>3428</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="C246" s="5" t="s">
         <v>3429</v>
-      </c>
-      <c r="C246" s="5" t="s">
-        <v>3430</v>
       </c>
       <c r="D246" s="5" t="s">
         <v>1251</v>
@@ -28975,13 +28972,13 @@
     </row>
     <row r="247">
       <c r="A247" s="5" t="s">
+        <v>3430</v>
+      </c>
+      <c r="B247" s="5" t="s">
         <v>3431</v>
       </c>
-      <c r="B247" s="5" t="s">
+      <c r="C247" s="5" t="s">
         <v>3432</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>3433</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>1251</v>
@@ -28989,13 +28986,13 @@
     </row>
     <row r="248">
       <c r="A248" s="5" t="s">
+        <v>3433</v>
+      </c>
+      <c r="B248" s="5" t="s">
         <v>3434</v>
       </c>
-      <c r="B248" s="5" t="s">
+      <c r="C248" s="5" t="s">
         <v>3435</v>
-      </c>
-      <c r="C248" s="5" t="s">
-        <v>3436</v>
       </c>
       <c r="D248" s="5" t="s">
         <v>1251</v>
@@ -29003,13 +29000,13 @@
     </row>
     <row r="249">
       <c r="A249" s="5" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B249" s="5" t="s">
         <v>3437</v>
       </c>
-      <c r="B249" s="5" t="s">
+      <c r="C249" s="5" t="s">
         <v>3438</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>3439</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>1251</v>
@@ -29017,13 +29014,13 @@
     </row>
     <row r="250">
       <c r="A250" s="5" t="s">
+        <v>3439</v>
+      </c>
+      <c r="B250" s="5" t="s">
         <v>3440</v>
       </c>
-      <c r="B250" s="5" t="s">
+      <c r="C250" s="5" t="s">
         <v>3441</v>
-      </c>
-      <c r="C250" s="5" t="s">
-        <v>3442</v>
       </c>
       <c r="D250" s="5" t="s">
         <v>1251</v>
@@ -29031,13 +29028,13 @@
     </row>
     <row r="251">
       <c r="A251" s="5" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B251" s="5" t="s">
         <v>3443</v>
       </c>
-      <c r="B251" s="5" t="s">
+      <c r="C251" s="5" t="s">
         <v>3444</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>3445</v>
       </c>
       <c r="D251" s="5" t="s">
         <v>1251</v>
@@ -29045,114 +29042,114 @@
     </row>
     <row r="252">
       <c r="A252" s="5" t="s">
+        <v>3445</v>
+      </c>
+      <c r="B252" s="5" t="s">
         <v>3446</v>
       </c>
-      <c r="B252" s="5" t="s">
+      <c r="C252" s="5" t="s">
         <v>3447</v>
       </c>
-      <c r="C252" s="5" t="s">
+      <c r="D252" s="5" t="s">
         <v>3448</v>
-      </c>
-      <c r="D252" s="5" t="s">
-        <v>3449</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="s">
+        <v>3449</v>
+      </c>
+      <c r="B253" s="5" t="s">
         <v>3450</v>
       </c>
-      <c r="B253" s="5" t="s">
+      <c r="C253" s="5" t="s">
         <v>3451</v>
       </c>
-      <c r="C253" s="5" t="s">
+      <c r="D253" s="5" t="s">
         <v>3452</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>3453</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="s">
+        <v>3453</v>
+      </c>
+      <c r="B254" s="5" t="s">
         <v>3454</v>
       </c>
-      <c r="B254" s="5" t="s">
+      <c r="C254" s="5" t="s">
         <v>3455</v>
       </c>
-      <c r="C254" s="5" t="s">
+      <c r="D254" s="5" t="s">
         <v>3456</v>
-      </c>
-      <c r="D254" s="5" t="s">
-        <v>3457</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B255" s="5" t="s">
         <v>3458</v>
       </c>
-      <c r="B255" s="5" t="s">
+      <c r="C255" s="5" t="s">
         <v>3459</v>
       </c>
-      <c r="C255" s="5" t="s">
-        <v>3460</v>
-      </c>
       <c r="D255" s="5" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B256" s="5" t="s">
         <v>3461</v>
       </c>
-      <c r="B256" s="5" t="s">
+      <c r="C256" s="5" t="s">
         <v>3462</v>
       </c>
-      <c r="C256" s="5" t="s">
-        <v>3463</v>
-      </c>
       <c r="D256" s="5" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="5" t="s">
+        <v>3463</v>
+      </c>
+      <c r="B257" s="5" t="s">
         <v>3464</v>
       </c>
-      <c r="B257" s="5" t="s">
+      <c r="C257" s="5" t="s">
         <v>3465</v>
       </c>
-      <c r="C257" s="5" t="s">
-        <v>3466</v>
-      </c>
       <c r="D257" s="5" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="s">
+        <v>3466</v>
+      </c>
+      <c r="B258" s="5" t="s">
         <v>3467</v>
       </c>
-      <c r="B258" s="5" t="s">
+      <c r="C258" s="5" t="s">
         <v>3468</v>
       </c>
-      <c r="C258" s="5" t="s">
-        <v>3469</v>
-      </c>
       <c r="D258" s="5" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="s">
+        <v>3469</v>
+      </c>
+      <c r="B259" s="5" t="s">
         <v>3470</v>
       </c>
-      <c r="B259" s="5" t="s">
+      <c r="C259" s="5" t="s">
         <v>3471</v>
       </c>
-      <c r="C259" s="5" t="s">
+      <c r="D259" s="5" t="s">
         <v>3472</v>
-      </c>
-      <c r="D259" s="5" t="s">
-        <v>3473</v>
       </c>
     </row>
     <row r="260">
@@ -29171,13 +29168,13 @@
     </row>
     <row r="261">
       <c r="A261" s="5" t="s">
+        <v>3473</v>
+      </c>
+      <c r="B261" s="5" t="s">
         <v>3474</v>
       </c>
-      <c r="B261" s="5" t="s">
+      <c r="C261" s="5" t="s">
         <v>3475</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>3476</v>
       </c>
       <c r="D261" s="5" t="s">
         <v>1363</v>
@@ -29185,80 +29182,80 @@
     </row>
     <row r="262">
       <c r="A262" s="5" t="s">
+        <v>3476</v>
+      </c>
+      <c r="B262" s="5" t="s">
         <v>3477</v>
       </c>
-      <c r="B262" s="5" t="s">
+      <c r="C262" s="5" t="s">
         <v>3478</v>
       </c>
-      <c r="C262" s="5" t="s">
+      <c r="D262" s="5" t="s">
         <v>3479</v>
-      </c>
-      <c r="D262" s="5" t="s">
-        <v>3480</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="5" t="s">
+        <v>3480</v>
+      </c>
+      <c r="B263" s="5" t="s">
         <v>3481</v>
       </c>
-      <c r="B263" s="5" t="s">
+      <c r="C263" s="5" t="s">
         <v>3482</v>
       </c>
-      <c r="C263" s="5" t="s">
-        <v>3483</v>
-      </c>
       <c r="D263" s="5" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="5" t="s">
+        <v>3483</v>
+      </c>
+      <c r="B264" s="5" t="s">
         <v>3484</v>
       </c>
-      <c r="B264" s="5" t="s">
+      <c r="C264" s="5" t="s">
         <v>3485</v>
       </c>
-      <c r="C264" s="5" t="s">
-        <v>3486</v>
-      </c>
       <c r="D264" s="5" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="5" t="s">
+        <v>3486</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C265" s="5" t="s">
         <v>3487</v>
       </c>
-      <c r="B265" s="5" t="s">
-        <v>3487</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>3488</v>
-      </c>
       <c r="D265" s="5" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="5" t="s">
+        <v>3488</v>
+      </c>
+      <c r="B266" s="5" t="s">
         <v>3489</v>
       </c>
-      <c r="B266" s="5" t="s">
+      <c r="C266" s="5" t="s">
         <v>3490</v>
       </c>
-      <c r="C266" s="5" t="s">
+      <c r="D266" s="5" t="s">
         <v>3491</v>
-      </c>
-      <c r="D266" s="5" t="s">
-        <v>3492</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="s">
+        <v>3492</v>
+      </c>
+      <c r="B267" s="5" t="s">
         <v>3493</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>3494</v>
       </c>
       <c r="C267" s="5" t="s">
         <v>1381</v>
@@ -29269,55 +29266,55 @@
     </row>
     <row r="268">
       <c r="A268" s="5" t="s">
+        <v>3494</v>
+      </c>
+      <c r="B268" s="5" t="s">
         <v>3495</v>
       </c>
-      <c r="B268" s="5" t="s">
+      <c r="C268" s="5" t="s">
         <v>3496</v>
       </c>
-      <c r="C268" s="5" t="s">
+      <c r="D268" s="5" t="s">
         <v>3497</v>
-      </c>
-      <c r="D268" s="5" t="s">
-        <v>3498</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="s">
+        <v>3498</v>
+      </c>
+      <c r="B269" s="5" t="s">
         <v>3499</v>
       </c>
-      <c r="B269" s="5" t="s">
+      <c r="C269" s="5" t="s">
         <v>3500</v>
       </c>
-      <c r="C269" s="5" t="s">
-        <v>3501</v>
-      </c>
       <c r="D269" s="5" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="s">
+        <v>3501</v>
+      </c>
+      <c r="B270" s="5" t="s">
         <v>3502</v>
       </c>
-      <c r="B270" s="5" t="s">
+      <c r="C270" s="5" t="s">
         <v>3503</v>
       </c>
-      <c r="C270" s="5" t="s">
+      <c r="D270" s="5" t="s">
         <v>3504</v>
-      </c>
-      <c r="D270" s="5" t="s">
-        <v>3505</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="5" t="s">
+        <v>3505</v>
+      </c>
+      <c r="B271" s="5" t="s">
         <v>3506</v>
       </c>
-      <c r="B271" s="5" t="s">
+      <c r="C271" s="5" t="s">
         <v>3507</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>3508</v>
       </c>
       <c r="D271" s="5" t="s">
         <v>1409</v>
@@ -29325,7 +29322,7 @@
     </row>
     <row r="272">
       <c r="A272" s="5" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="B272" s="5" t="s">
         <v>1407</v>
@@ -29339,10 +29336,10 @@
     </row>
     <row r="273">
       <c r="A273" s="5" t="s">
+        <v>3509</v>
+      </c>
+      <c r="B273" s="5" t="s">
         <v>3510</v>
-      </c>
-      <c r="B273" s="5" t="s">
-        <v>3511</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>1412</v>
@@ -29353,41 +29350,41 @@
     </row>
     <row r="274">
       <c r="A274" s="5" t="s">
+        <v>3511</v>
+      </c>
+      <c r="B274" s="5" t="s">
         <v>3512</v>
       </c>
-      <c r="B274" s="5" t="s">
+      <c r="C274" s="5" t="s">
         <v>3513</v>
       </c>
-      <c r="C274" s="5" t="s">
+      <c r="D274" s="5" t="s">
         <v>3514</v>
-      </c>
-      <c r="D274" s="5" t="s">
-        <v>3515</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="5" t="s">
+        <v>3515</v>
+      </c>
+      <c r="B275" s="5" t="s">
         <v>3516</v>
       </c>
-      <c r="B275" s="5" t="s">
+      <c r="C275" s="5" t="s">
         <v>3517</v>
       </c>
-      <c r="C275" s="5" t="s">
+      <c r="D275" s="5" t="s">
         <v>3518</v>
-      </c>
-      <c r="D275" s="5" t="s">
-        <v>3519</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="s">
+        <v>3519</v>
+      </c>
+      <c r="B276" s="5" t="s">
         <v>3520</v>
       </c>
-      <c r="B276" s="5" t="s">
+      <c r="C276" s="5" t="s">
         <v>3521</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>3522</v>
       </c>
       <c r="D276" s="5" t="s">
         <v>1446</v>
@@ -29395,7 +29392,7 @@
     </row>
     <row r="277">
       <c r="A277" s="5" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="B277" s="5" t="s">
         <v>1451</v>
@@ -29423,27 +29420,27 @@
     </row>
     <row r="279">
       <c r="A279" s="5" t="s">
+        <v>3523</v>
+      </c>
+      <c r="B279" s="5" t="s">
         <v>3524</v>
       </c>
-      <c r="B279" s="5" t="s">
+      <c r="C279" s="5" t="s">
         <v>3525</v>
       </c>
-      <c r="C279" s="5" t="s">
+      <c r="D279" s="5" t="s">
         <v>3526</v>
-      </c>
-      <c r="D279" s="5" t="s">
-        <v>3527</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="5" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B280" s="5" t="s">
         <v>3528</v>
       </c>
-      <c r="B280" s="5" t="s">
+      <c r="C280" s="5" t="s">
         <v>3529</v>
-      </c>
-      <c r="C280" s="5" t="s">
-        <v>3530</v>
       </c>
       <c r="D280" s="5" t="s">
         <v>1462</v>
@@ -29451,13 +29448,13 @@
     </row>
     <row r="281">
       <c r="A281" s="5" t="s">
+        <v>3530</v>
+      </c>
+      <c r="B281" s="5" t="s">
         <v>3531</v>
       </c>
-      <c r="B281" s="5" t="s">
+      <c r="C281" s="5" t="s">
         <v>3532</v>
-      </c>
-      <c r="C281" s="5" t="s">
-        <v>3533</v>
       </c>
       <c r="D281" s="5" t="s">
         <v>1462</v>
@@ -29465,13 +29462,13 @@
     </row>
     <row r="282">
       <c r="A282" s="5" t="s">
+        <v>3533</v>
+      </c>
+      <c r="B282" s="5" t="s">
         <v>3534</v>
       </c>
-      <c r="B282" s="5" t="s">
+      <c r="C282" s="5" t="s">
         <v>3535</v>
-      </c>
-      <c r="C282" s="5" t="s">
-        <v>3536</v>
       </c>
       <c r="D282" s="5" t="s">
         <v>1462</v>
@@ -29479,13 +29476,13 @@
     </row>
     <row r="283">
       <c r="A283" s="5" t="s">
+        <v>3536</v>
+      </c>
+      <c r="B283" s="5" t="s">
         <v>3537</v>
       </c>
-      <c r="B283" s="5" t="s">
+      <c r="C283" s="5" t="s">
         <v>3538</v>
-      </c>
-      <c r="C283" s="5" t="s">
-        <v>3539</v>
       </c>
       <c r="D283" s="5" t="s">
         <v>1462</v>
@@ -29493,13 +29490,13 @@
     </row>
     <row r="284">
       <c r="A284" s="5" t="s">
+        <v>3539</v>
+      </c>
+      <c r="B284" s="5" t="s">
         <v>3540</v>
       </c>
-      <c r="B284" s="5" t="s">
+      <c r="C284" s="5" t="s">
         <v>3541</v>
-      </c>
-      <c r="C284" s="5" t="s">
-        <v>3542</v>
       </c>
       <c r="D284" s="5" t="s">
         <v>1462</v>
@@ -29507,13 +29504,13 @@
     </row>
     <row r="285">
       <c r="A285" s="5" t="s">
+        <v>3542</v>
+      </c>
+      <c r="B285" s="5" t="s">
         <v>3543</v>
       </c>
-      <c r="B285" s="5" t="s">
+      <c r="C285" s="5" t="s">
         <v>3544</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>3545</v>
       </c>
       <c r="D285" s="5" t="s">
         <v>1462</v>
@@ -29521,13 +29518,13 @@
     </row>
     <row r="286">
       <c r="A286" s="5" t="s">
+        <v>3545</v>
+      </c>
+      <c r="B286" s="5" t="s">
         <v>3546</v>
       </c>
-      <c r="B286" s="5" t="s">
+      <c r="C286" s="5" t="s">
         <v>3547</v>
-      </c>
-      <c r="C286" s="5" t="s">
-        <v>3548</v>
       </c>
       <c r="D286" s="5" t="s">
         <v>1462</v>
@@ -29535,13 +29532,13 @@
     </row>
     <row r="287">
       <c r="A287" s="5" t="s">
+        <v>3548</v>
+      </c>
+      <c r="B287" s="5" t="s">
         <v>3549</v>
       </c>
-      <c r="B287" s="5" t="s">
+      <c r="C287" s="5" t="s">
         <v>3550</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>3551</v>
       </c>
       <c r="D287" s="5" t="s">
         <v>1462</v>
@@ -29549,13 +29546,13 @@
     </row>
     <row r="288">
       <c r="A288" s="5" t="s">
+        <v>3551</v>
+      </c>
+      <c r="B288" s="5" t="s">
         <v>3552</v>
       </c>
-      <c r="B288" s="5" t="s">
+      <c r="C288" s="5" t="s">
         <v>3553</v>
-      </c>
-      <c r="C288" s="5" t="s">
-        <v>3554</v>
       </c>
       <c r="D288" s="5" t="s">
         <v>1462</v>
@@ -29563,7 +29560,7 @@
     </row>
     <row r="289">
       <c r="A289" s="5" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>1488</v>
@@ -29577,7 +29574,7 @@
     </row>
     <row r="290">
       <c r="A290" s="5" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>1509</v>
@@ -29591,13 +29588,13 @@
     </row>
     <row r="291">
       <c r="A291" s="5" t="s">
+        <v>3556</v>
+      </c>
+      <c r="B291" s="5" t="s">
         <v>3557</v>
       </c>
-      <c r="B291" s="5" t="s">
+      <c r="C291" s="5" t="s">
         <v>3558</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>3559</v>
       </c>
       <c r="D291" s="5" t="s">
         <v>1518</v>
@@ -29605,7 +29602,7 @@
     </row>
     <row r="292">
       <c r="A292" s="5" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>1516</v>
@@ -29619,27 +29616,27 @@
     </row>
     <row r="293">
       <c r="A293" s="5" t="s">
+        <v>3560</v>
+      </c>
+      <c r="B293" s="5" t="s">
         <v>3561</v>
       </c>
-      <c r="B293" s="5" t="s">
+      <c r="C293" s="5" t="s">
         <v>3562</v>
       </c>
-      <c r="C293" s="5" t="s">
+      <c r="D293" s="5" t="s">
         <v>3563</v>
-      </c>
-      <c r="D293" s="5" t="s">
-        <v>3564</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="s">
+        <v>3564</v>
+      </c>
+      <c r="B294" s="5" t="s">
         <v>3565</v>
       </c>
-      <c r="B294" s="5" t="s">
+      <c r="C294" s="5" t="s">
         <v>3566</v>
-      </c>
-      <c r="C294" s="5" t="s">
-        <v>3567</v>
       </c>
       <c r="D294" s="5" t="s">
         <v>1535</v>
@@ -29647,13 +29644,13 @@
     </row>
     <row r="295">
       <c r="A295" s="5" t="s">
+        <v>3567</v>
+      </c>
+      <c r="B295" s="5" t="s">
         <v>3568</v>
       </c>
-      <c r="B295" s="5" t="s">
+      <c r="C295" s="5" t="s">
         <v>3569</v>
-      </c>
-      <c r="C295" s="5" t="s">
-        <v>3570</v>
       </c>
       <c r="D295" s="5" t="s">
         <v>1543</v>
@@ -29661,7 +29658,7 @@
     </row>
     <row r="296">
       <c r="A296" s="5" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>1541</v>
@@ -29675,7 +29672,7 @@
     </row>
     <row r="297">
       <c r="A297" s="5" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>1545</v>
@@ -29689,27 +29686,27 @@
     </row>
     <row r="298">
       <c r="A298" s="5" t="s">
+        <v>3572</v>
+      </c>
+      <c r="B298" s="5" t="s">
         <v>3573</v>
       </c>
-      <c r="B298" s="5" t="s">
+      <c r="C298" s="5" t="s">
         <v>3574</v>
       </c>
-      <c r="C298" s="5" t="s">
+      <c r="D298" s="5" t="s">
         <v>3575</v>
-      </c>
-      <c r="D298" s="5" t="s">
-        <v>3576</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="s">
+        <v>3576</v>
+      </c>
+      <c r="B299" s="5" t="s">
         <v>3577</v>
       </c>
-      <c r="B299" s="5" t="s">
+      <c r="C299" s="5" t="s">
         <v>3578</v>
-      </c>
-      <c r="C299" s="5" t="s">
-        <v>3579</v>
       </c>
       <c r="D299" s="5" t="s">
         <v>1573</v>
@@ -29717,7 +29714,7 @@
     </row>
     <row r="300">
       <c r="A300" s="5" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>1651</v>
@@ -29731,7 +29728,7 @@
     </row>
     <row r="301">
       <c r="A301" s="5" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>1655</v>
@@ -29745,10 +29742,10 @@
     </row>
     <row r="302">
       <c r="A302" s="5" t="s">
+        <v>3581</v>
+      </c>
+      <c r="B302" s="5" t="s">
         <v>3582</v>
-      </c>
-      <c r="B302" s="5" t="s">
-        <v>3583</v>
       </c>
       <c r="C302" s="5" t="s">
         <v>1659</v>
@@ -29759,24 +29756,24 @@
     </row>
     <row r="303">
       <c r="A303" s="5" t="s">
+        <v>3583</v>
+      </c>
+      <c r="B303" s="5" t="s">
         <v>3584</v>
       </c>
-      <c r="B303" s="5" t="s">
+      <c r="C303" s="5" t="s">
         <v>3585</v>
       </c>
-      <c r="C303" s="5" t="s">
+      <c r="D303" s="5" t="s">
         <v>3586</v>
-      </c>
-      <c r="D303" s="5" t="s">
-        <v>3587</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="5" t="s">
+        <v>3587</v>
+      </c>
+      <c r="B304" s="5" t="s">
         <v>3588</v>
-      </c>
-      <c r="B304" s="5" t="s">
-        <v>3589</v>
       </c>
       <c r="C304" s="5" t="s">
         <v>577</v>
@@ -29787,7 +29784,7 @@
     </row>
     <row r="305">
       <c r="A305" s="5" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>1674</v>
@@ -29801,13 +29798,13 @@
     </row>
     <row r="306">
       <c r="A306" s="5" t="s">
+        <v>3590</v>
+      </c>
+      <c r="B306" s="5" t="s">
         <v>3591</v>
       </c>
-      <c r="B306" s="5" t="s">
+      <c r="C306" s="5" t="s">
         <v>3592</v>
-      </c>
-      <c r="C306" s="5" t="s">
-        <v>3593</v>
       </c>
       <c r="D306" s="5" t="s">
         <v>1680</v>
@@ -29815,13 +29812,13 @@
     </row>
     <row r="307">
       <c r="A307" s="5" t="s">
+        <v>3593</v>
+      </c>
+      <c r="B307" s="5" t="s">
         <v>3594</v>
       </c>
-      <c r="B307" s="5" t="s">
+      <c r="C307" s="5" t="s">
         <v>3595</v>
-      </c>
-      <c r="C307" s="5" t="s">
-        <v>3596</v>
       </c>
       <c r="D307" s="5" t="s">
         <v>1680</v>
@@ -29829,13 +29826,13 @@
     </row>
     <row r="308">
       <c r="A308" s="5" t="s">
+        <v>3596</v>
+      </c>
+      <c r="B308" s="5" t="s">
         <v>3597</v>
       </c>
-      <c r="B308" s="5" t="s">
+      <c r="C308" s="5" t="s">
         <v>3598</v>
-      </c>
-      <c r="C308" s="5" t="s">
-        <v>3599</v>
       </c>
       <c r="D308" s="5" t="s">
         <v>1680</v>
@@ -29843,13 +29840,13 @@
     </row>
     <row r="309">
       <c r="A309" s="5" t="s">
+        <v>3599</v>
+      </c>
+      <c r="B309" s="5" t="s">
         <v>3600</v>
       </c>
-      <c r="B309" s="5" t="s">
+      <c r="C309" s="5" t="s">
         <v>3601</v>
-      </c>
-      <c r="C309" s="5" t="s">
-        <v>3602</v>
       </c>
       <c r="D309" s="5" t="s">
         <v>1680</v>
@@ -29857,13 +29854,13 @@
     </row>
     <row r="310">
       <c r="A310" s="5" t="s">
+        <v>3602</v>
+      </c>
+      <c r="B310" s="5" t="s">
         <v>3603</v>
       </c>
-      <c r="B310" s="5" t="s">
+      <c r="C310" s="5" t="s">
         <v>3604</v>
-      </c>
-      <c r="C310" s="5" t="s">
-        <v>3605</v>
       </c>
       <c r="D310" s="5" t="s">
         <v>1680</v>
@@ -29871,7 +29868,7 @@
     </row>
     <row r="311">
       <c r="A311" s="5" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>1703</v>
@@ -29885,13 +29882,13 @@
     </row>
     <row r="312">
       <c r="A312" s="5" t="s">
+        <v>3606</v>
+      </c>
+      <c r="B312" s="5" t="s">
         <v>3607</v>
       </c>
-      <c r="B312" s="5" t="s">
+      <c r="C312" s="5" t="s">
         <v>3608</v>
-      </c>
-      <c r="C312" s="5" t="s">
-        <v>3609</v>
       </c>
       <c r="D312" s="5" t="s">
         <v>1680</v>
@@ -29899,13 +29896,13 @@
     </row>
     <row r="313">
       <c r="A313" s="5" t="s">
+        <v>3609</v>
+      </c>
+      <c r="B313" s="5" t="s">
         <v>3610</v>
       </c>
-      <c r="B313" s="5" t="s">
+      <c r="C313" s="5" t="s">
         <v>3611</v>
-      </c>
-      <c r="C313" s="5" t="s">
-        <v>3612</v>
       </c>
       <c r="D313" s="5" t="s">
         <v>1680</v>
@@ -29913,13 +29910,13 @@
     </row>
     <row r="314">
       <c r="A314" s="5" t="s">
+        <v>3612</v>
+      </c>
+      <c r="B314" s="5" t="s">
         <v>3613</v>
       </c>
-      <c r="B314" s="5" t="s">
+      <c r="C314" s="5" t="s">
         <v>3614</v>
-      </c>
-      <c r="C314" s="5" t="s">
-        <v>3615</v>
       </c>
       <c r="D314" s="5" t="s">
         <v>1680</v>
@@ -29927,13 +29924,13 @@
     </row>
     <row r="315">
       <c r="A315" s="5" t="s">
+        <v>3615</v>
+      </c>
+      <c r="B315" s="5" t="s">
         <v>3616</v>
       </c>
-      <c r="B315" s="5" t="s">
+      <c r="C315" s="5" t="s">
         <v>3617</v>
-      </c>
-      <c r="C315" s="5" t="s">
-        <v>3618</v>
       </c>
       <c r="D315" s="5" t="s">
         <v>1680</v>
@@ -29941,7 +29938,7 @@
     </row>
     <row r="316">
       <c r="A316" s="5" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="B316" s="5" t="s">
         <v>1712</v>
@@ -29955,13 +29952,13 @@
     </row>
     <row r="317">
       <c r="A317" s="5" t="s">
+        <v>3619</v>
+      </c>
+      <c r="B317" s="5" t="s">
         <v>3620</v>
       </c>
-      <c r="B317" s="5" t="s">
+      <c r="C317" s="5" t="s">
         <v>3621</v>
-      </c>
-      <c r="C317" s="5" t="s">
-        <v>3622</v>
       </c>
       <c r="D317" s="5" t="s">
         <v>1680</v>
@@ -29969,10 +29966,10 @@
     </row>
     <row r="318">
       <c r="A318" s="5" t="s">
+        <v>3622</v>
+      </c>
+      <c r="B318" s="5" t="s">
         <v>3623</v>
-      </c>
-      <c r="B318" s="5" t="s">
-        <v>3624</v>
       </c>
       <c r="C318" s="5" t="s">
         <v>1742</v>
@@ -29983,7 +29980,7 @@
     </row>
     <row r="319">
       <c r="A319" s="5" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>1726</v>
@@ -29997,7 +29994,7 @@
     </row>
     <row r="320">
       <c r="A320" s="5" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>1732</v>
@@ -30011,13 +30008,13 @@
     </row>
     <row r="321">
       <c r="A321" s="5" t="s">
+        <v>3626</v>
+      </c>
+      <c r="B321" s="5" t="s">
         <v>3627</v>
       </c>
-      <c r="B321" s="5" t="s">
+      <c r="C321" s="5" t="s">
         <v>3628</v>
-      </c>
-      <c r="C321" s="5" t="s">
-        <v>3629</v>
       </c>
       <c r="D321" s="5" t="s">
         <v>1724</v>
@@ -30025,10 +30022,10 @@
     </row>
     <row r="322">
       <c r="A322" s="5" t="s">
+        <v>3629</v>
+      </c>
+      <c r="B322" s="5" t="s">
         <v>3630</v>
-      </c>
-      <c r="B322" s="5" t="s">
-        <v>3631</v>
       </c>
       <c r="C322" s="5" t="s">
         <v>1745</v>
@@ -30053,13 +30050,13 @@
     </row>
     <row r="324">
       <c r="A324" s="5" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B324" s="5" t="s">
         <v>3632</v>
       </c>
-      <c r="B324" s="5" t="s">
+      <c r="C324" s="5" t="s">
         <v>3633</v>
-      </c>
-      <c r="C324" s="5" t="s">
-        <v>3634</v>
       </c>
       <c r="D324" s="5" t="s">
         <v>1724</v>
@@ -30067,13 +30064,13 @@
     </row>
     <row r="325">
       <c r="A325" s="5" t="s">
+        <v>3634</v>
+      </c>
+      <c r="B325" s="5" t="s">
         <v>3635</v>
       </c>
-      <c r="B325" s="5" t="s">
+      <c r="C325" s="5" t="s">
         <v>3636</v>
-      </c>
-      <c r="C325" s="5" t="s">
-        <v>3637</v>
       </c>
       <c r="D325" s="5" t="s">
         <v>1724</v>
@@ -30081,13 +30078,13 @@
     </row>
     <row r="326">
       <c r="A326" s="5" t="s">
+        <v>3637</v>
+      </c>
+      <c r="B326" s="5" t="s">
         <v>3638</v>
       </c>
-      <c r="B326" s="5" t="s">
+      <c r="C326" s="5" t="s">
         <v>3639</v>
-      </c>
-      <c r="C326" s="5" t="s">
-        <v>3640</v>
       </c>
       <c r="D326" s="5" t="s">
         <v>1764</v>
@@ -30095,13 +30092,13 @@
     </row>
     <row r="327">
       <c r="A327" s="5" t="s">
+        <v>3640</v>
+      </c>
+      <c r="B327" s="5" t="s">
         <v>3641</v>
       </c>
-      <c r="B327" s="5" t="s">
+      <c r="C327" s="5" t="s">
         <v>3642</v>
-      </c>
-      <c r="C327" s="5" t="s">
-        <v>3643</v>
       </c>
       <c r="D327" s="5" t="s">
         <v>1764</v>
@@ -30109,7 +30106,7 @@
     </row>
     <row r="328">
       <c r="A328" s="5" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="B328" s="5" t="s">
         <v>1766</v>
@@ -30123,7 +30120,7 @@
     </row>
     <row r="329">
       <c r="A329" s="5" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="B329" s="5" t="s">
         <v>1770</v>
@@ -30137,13 +30134,13 @@
     </row>
     <row r="330">
       <c r="A330" s="5" t="s">
+        <v>3645</v>
+      </c>
+      <c r="B330" s="5" t="s">
         <v>3646</v>
       </c>
-      <c r="B330" s="5" t="s">
+      <c r="C330" s="5" t="s">
         <v>3647</v>
-      </c>
-      <c r="C330" s="5" t="s">
-        <v>3648</v>
       </c>
       <c r="D330" s="5" t="s">
         <v>1768</v>
@@ -30151,35 +30148,35 @@
     </row>
     <row r="331">
       <c r="A331" s="5" t="s">
+        <v>3648</v>
+      </c>
+      <c r="B331" s="5" t="s">
         <v>3649</v>
       </c>
-      <c r="B331" s="5" t="s">
+      <c r="C331" s="5" t="s">
         <v>3650</v>
       </c>
-      <c r="C331" s="5" t="s">
+      <c r="D331" s="5" t="s">
         <v>3651</v>
-      </c>
-      <c r="D331" s="5" t="s">
-        <v>3652</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="5" t="s">
+        <v>3652</v>
+      </c>
+      <c r="B332" s="5" t="s">
         <v>3653</v>
       </c>
-      <c r="B332" s="5" t="s">
+      <c r="C332" s="5" t="s">
         <v>3654</v>
       </c>
-      <c r="C332" s="5" t="s">
+      <c r="D332" s="5" t="s">
         <v>3655</v>
-      </c>
-      <c r="D332" s="5" t="s">
-        <v>3656</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="5" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>1823</v>
@@ -30193,13 +30190,13 @@
     </row>
     <row r="334">
       <c r="A334" s="5" t="s">
+        <v>3657</v>
+      </c>
+      <c r="B334" s="5" t="s">
         <v>3658</v>
       </c>
-      <c r="B334" s="5" t="s">
+      <c r="C334" s="5" t="s">
         <v>3659</v>
-      </c>
-      <c r="C334" s="5" t="s">
-        <v>3660</v>
       </c>
       <c r="D334" s="5" t="s">
         <v>1840</v>
@@ -30207,13 +30204,13 @@
     </row>
     <row r="335">
       <c r="A335" s="5" t="s">
+        <v>3660</v>
+      </c>
+      <c r="B335" s="5" t="s">
         <v>3661</v>
       </c>
-      <c r="B335" s="5" t="s">
+      <c r="C335" s="5" t="s">
         <v>3662</v>
-      </c>
-      <c r="C335" s="5" t="s">
-        <v>3663</v>
       </c>
       <c r="D335" s="5" t="s">
         <v>1844</v>
@@ -30221,49 +30218,49 @@
     </row>
     <row r="336">
       <c r="A336" s="5" t="s">
+        <v>3663</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>3663</v>
+      </c>
+      <c r="C336" s="5" t="s">
         <v>3664</v>
       </c>
-      <c r="B336" s="5" t="s">
-        <v>3664</v>
-      </c>
-      <c r="C336" s="5" t="s">
-        <v>3665</v>
-      </c>
       <c r="D336" s="5" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="s">
+        <v>3665</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>3665</v>
+      </c>
+      <c r="C337" s="5" t="s">
         <v>3666</v>
       </c>
-      <c r="B337" s="5" t="s">
-        <v>3666</v>
-      </c>
-      <c r="C337" s="5" t="s">
-        <v>3667</v>
-      </c>
       <c r="D337" s="5" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="5" t="s">
+        <v>3667</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>3667</v>
+      </c>
+      <c r="C338" s="5" t="s">
         <v>3668</v>
       </c>
-      <c r="B338" s="5" t="s">
-        <v>3668</v>
-      </c>
-      <c r="C338" s="5" t="s">
-        <v>3669</v>
-      </c>
       <c r="D338" s="5" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="5" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="B339" s="5" t="s">
         <v>1846</v>
@@ -30277,7 +30274,7 @@
     </row>
     <row r="340">
       <c r="A340" s="5" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="B340" s="5" t="s">
         <v>1850</v>
@@ -30291,13 +30288,13 @@
     </row>
     <row r="341">
       <c r="A341" s="5" t="s">
+        <v>3671</v>
+      </c>
+      <c r="B341" s="5" t="s">
         <v>3672</v>
       </c>
-      <c r="B341" s="5" t="s">
+      <c r="C341" s="5" t="s">
         <v>3673</v>
-      </c>
-      <c r="C341" s="5" t="s">
-        <v>3674</v>
       </c>
       <c r="D341" s="5" t="s">
         <v>1855</v>
@@ -30305,7 +30302,7 @@
     </row>
     <row r="342">
       <c r="A342" s="5" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>1853</v>
@@ -30319,41 +30316,41 @@
     </row>
     <row r="343">
       <c r="A343" s="5" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>3675</v>
+      </c>
+      <c r="C343" s="5" t="s">
         <v>3676</v>
       </c>
-      <c r="B343" s="5" t="s">
-        <v>3676</v>
-      </c>
-      <c r="C343" s="5" t="s">
-        <v>3677</v>
-      </c>
       <c r="D343" s="5" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="5" t="s">
+        <v>3677</v>
+      </c>
+      <c r="B344" s="5" t="s">
         <v>3678</v>
       </c>
-      <c r="B344" s="5" t="s">
+      <c r="C344" s="5" t="s">
         <v>3679</v>
       </c>
-      <c r="C344" s="5" t="s">
+      <c r="D344" s="5" t="s">
         <v>3680</v>
-      </c>
-      <c r="D344" s="5" t="s">
-        <v>3681</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="5" t="s">
+        <v>3681</v>
+      </c>
+      <c r="B345" s="5" t="s">
         <v>3682</v>
       </c>
-      <c r="B345" s="5" t="s">
+      <c r="C345" s="5" t="s">
         <v>3683</v>
-      </c>
-      <c r="C345" s="5" t="s">
-        <v>3684</v>
       </c>
       <c r="D345" s="5" t="s">
         <v>1859</v>
@@ -30361,13 +30358,13 @@
     </row>
     <row r="346">
       <c r="A346" s="5" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B346" s="5" t="s">
         <v>3685</v>
       </c>
-      <c r="B346" s="5" t="s">
+      <c r="C346" s="5" t="s">
         <v>3686</v>
-      </c>
-      <c r="C346" s="5" t="s">
-        <v>3687</v>
       </c>
       <c r="D346" s="5" t="s">
         <v>1859</v>
@@ -30389,35 +30386,35 @@
     </row>
     <row r="348">
       <c r="A348" s="5" t="s">
+        <v>3687</v>
+      </c>
+      <c r="B348" s="5" t="s">
         <v>3688</v>
       </c>
-      <c r="B348" s="5" t="s">
+      <c r="C348" s="5" t="s">
         <v>3689</v>
       </c>
-      <c r="C348" s="5" t="s">
+      <c r="D348" s="5" t="s">
         <v>3690</v>
-      </c>
-      <c r="D348" s="5" t="s">
-        <v>3691</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="5" t="s">
+        <v>3691</v>
+      </c>
+      <c r="B349" s="5" t="s">
         <v>3692</v>
       </c>
-      <c r="B349" s="5" t="s">
+      <c r="C349" s="5" t="s">
         <v>3693</v>
       </c>
-      <c r="C349" s="5" t="s">
-        <v>3694</v>
-      </c>
       <c r="D349" s="5" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="5" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="B350" s="5" t="s">
         <v>1909</v>
@@ -30431,44 +30428,44 @@
     </row>
     <row r="351">
       <c r="A351" s="5" t="s">
+        <v>3695</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>3695</v>
+      </c>
+      <c r="C351" s="5" t="s">
         <v>3696</v>
       </c>
-      <c r="B351" s="5" t="s">
-        <v>3696</v>
-      </c>
-      <c r="C351" s="5" t="s">
-        <v>3697</v>
-      </c>
       <c r="D351" s="5" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="5" t="s">
+        <v>3697</v>
+      </c>
+      <c r="B352" s="5" t="s">
         <v>3698</v>
       </c>
-      <c r="B352" s="5" t="s">
+      <c r="C352" s="5" t="s">
         <v>3699</v>
       </c>
-      <c r="C352" s="5" t="s">
+      <c r="D352" s="5" t="s">
         <v>3700</v>
-      </c>
-      <c r="D352" s="5" t="s">
-        <v>3701</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="5" t="s">
+        <v>3701</v>
+      </c>
+      <c r="B353" s="5" t="s">
         <v>3702</v>
       </c>
-      <c r="B353" s="5" t="s">
+      <c r="C353" s="5" t="s">
         <v>3703</v>
       </c>
-      <c r="C353" s="5" t="s">
+      <c r="D353" s="5" t="s">
         <v>3704</v>
-      </c>
-      <c r="D353" s="5" t="s">
-        <v>3705</v>
       </c>
     </row>
     <row r="354">
@@ -30487,16 +30484,16 @@
     </row>
     <row r="355">
       <c r="A355" s="5" t="s">
+        <v>3705</v>
+      </c>
+      <c r="B355" s="5" t="s">
         <v>3706</v>
-      </c>
-      <c r="B355" s="5" t="s">
-        <v>3707</v>
       </c>
       <c r="C355" s="5" t="s">
         <v>1739</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="356">
@@ -30515,13 +30512,13 @@
     </row>
     <row r="357">
       <c r="A357" s="5" t="s">
+        <v>3708</v>
+      </c>
+      <c r="B357" s="5" t="s">
         <v>3709</v>
       </c>
-      <c r="B357" s="5" t="s">
+      <c r="C357" s="5" t="s">
         <v>3710</v>
-      </c>
-      <c r="C357" s="5" t="s">
-        <v>3711</v>
       </c>
       <c r="D357" s="5" t="s">
         <v>1927</v>
@@ -30529,10 +30526,10 @@
     </row>
     <row r="358">
       <c r="A358" s="5" t="s">
+        <v>3711</v>
+      </c>
+      <c r="B358" s="5" t="s">
         <v>3712</v>
-      </c>
-      <c r="B358" s="5" t="s">
-        <v>3713</v>
       </c>
       <c r="C358" s="5" t="s">
         <v>1939</v>
@@ -30543,7 +30540,7 @@
     </row>
     <row r="359">
       <c r="A359" s="5" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>1942</v>
@@ -30557,7 +30554,7 @@
     </row>
     <row r="360">
       <c r="A360" s="5" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>1945</v>
@@ -30571,7 +30568,7 @@
     </row>
     <row r="361">
       <c r="A361" s="5" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>1948</v>
@@ -30585,7 +30582,7 @@
     </row>
     <row r="362">
       <c r="A362" s="5" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>1951</v>
@@ -30599,7 +30596,7 @@
     </row>
     <row r="363">
       <c r="A363" s="5" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>1954</v>
@@ -30613,13 +30610,13 @@
     </row>
     <row r="364">
       <c r="A364" s="5" t="s">
+        <v>3718</v>
+      </c>
+      <c r="B364" s="5" t="s">
         <v>3719</v>
       </c>
-      <c r="B364" s="5" t="s">
+      <c r="C364" s="5" t="s">
         <v>3720</v>
-      </c>
-      <c r="C364" s="5" t="s">
-        <v>3721</v>
       </c>
       <c r="D364" s="5" t="s">
         <v>1940</v>
@@ -30627,7 +30624,7 @@
     </row>
     <row r="365">
       <c r="A365" s="5" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>1957</v>
@@ -30641,7 +30638,7 @@
     </row>
     <row r="366">
       <c r="A366" s="5" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>1960</v>
@@ -30655,13 +30652,13 @@
     </row>
     <row r="367">
       <c r="A367" s="5" t="s">
+        <v>3723</v>
+      </c>
+      <c r="B367" s="5" t="s">
         <v>3724</v>
       </c>
-      <c r="B367" s="5" t="s">
+      <c r="C367" s="5" t="s">
         <v>3725</v>
-      </c>
-      <c r="C367" s="5" t="s">
-        <v>3726</v>
       </c>
       <c r="D367" s="5" t="s">
         <v>1940</v>
@@ -30669,13 +30666,13 @@
     </row>
     <row r="368">
       <c r="A368" s="5" t="s">
+        <v>3726</v>
+      </c>
+      <c r="B368" s="5" t="s">
         <v>3727</v>
       </c>
-      <c r="B368" s="5" t="s">
+      <c r="C368" s="5" t="s">
         <v>3728</v>
-      </c>
-      <c r="C368" s="5" t="s">
-        <v>3729</v>
       </c>
       <c r="D368" s="5" t="s">
         <v>1940</v>
@@ -30697,13 +30694,13 @@
     </row>
     <row r="370">
       <c r="A370" s="5" t="s">
+        <v>3729</v>
+      </c>
+      <c r="B370" s="5" t="s">
         <v>3730</v>
       </c>
-      <c r="B370" s="5" t="s">
+      <c r="C370" s="5" t="s">
         <v>3731</v>
-      </c>
-      <c r="C370" s="5" t="s">
-        <v>3732</v>
       </c>
       <c r="D370" s="5" t="s">
         <v>1940</v>
@@ -30711,13 +30708,13 @@
     </row>
     <row r="371">
       <c r="A371" s="5" t="s">
+        <v>3732</v>
+      </c>
+      <c r="B371" s="5" t="s">
         <v>3733</v>
       </c>
-      <c r="B371" s="5" t="s">
+      <c r="C371" s="5" t="s">
         <v>3734</v>
-      </c>
-      <c r="C371" s="5" t="s">
-        <v>3735</v>
       </c>
       <c r="D371" s="5" t="s">
         <v>1940</v>
@@ -30725,13 +30722,13 @@
     </row>
     <row r="372">
       <c r="A372" s="5" t="s">
+        <v>3735</v>
+      </c>
+      <c r="B372" s="5" t="s">
         <v>3736</v>
       </c>
-      <c r="B372" s="5" t="s">
+      <c r="C372" s="5" t="s">
         <v>3737</v>
-      </c>
-      <c r="C372" s="5" t="s">
-        <v>3738</v>
       </c>
       <c r="D372" s="5" t="s">
         <v>1940</v>
@@ -30739,7 +30736,7 @@
     </row>
     <row r="373">
       <c r="A373" s="5" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>1966</v>
@@ -30753,13 +30750,13 @@
     </row>
     <row r="374">
       <c r="A374" s="5" t="s">
+        <v>3739</v>
+      </c>
+      <c r="B374" s="5" t="s">
         <v>3740</v>
       </c>
-      <c r="B374" s="5" t="s">
+      <c r="C374" s="5" t="s">
         <v>3741</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>3742</v>
       </c>
       <c r="D374" s="5" t="s">
         <v>1940</v>
@@ -30767,13 +30764,13 @@
     </row>
     <row r="375">
       <c r="A375" s="5" t="s">
+        <v>3742</v>
+      </c>
+      <c r="B375" s="5" t="s">
         <v>3743</v>
       </c>
-      <c r="B375" s="5" t="s">
+      <c r="C375" s="5" t="s">
         <v>3744</v>
-      </c>
-      <c r="C375" s="5" t="s">
-        <v>3745</v>
       </c>
       <c r="D375" s="5" t="s">
         <v>1940</v>
@@ -30781,7 +30778,7 @@
     </row>
     <row r="376">
       <c r="A376" s="5" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
       <c r="B376" s="5" t="s">
         <v>1969</v>
@@ -30795,7 +30792,7 @@
     </row>
     <row r="377">
       <c r="A377" s="5" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>1972</v>
@@ -30809,195 +30806,195 @@
     </row>
     <row r="378">
       <c r="A378" s="5" t="s">
+        <v>3747</v>
+      </c>
+      <c r="B378" s="5" t="s">
         <v>3748</v>
       </c>
-      <c r="B378" s="5" t="s">
+      <c r="C378" s="5" t="s">
         <v>3749</v>
       </c>
-      <c r="C378" s="5" t="s">
+      <c r="D378" s="5" t="s">
         <v>3750</v>
-      </c>
-      <c r="D378" s="5" t="s">
-        <v>3751</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="5" t="s">
+        <v>3751</v>
+      </c>
+      <c r="B379" s="5" t="s">
         <v>3752</v>
       </c>
-      <c r="B379" s="5" t="s">
+      <c r="C379" s="5" t="s">
         <v>3753</v>
       </c>
-      <c r="C379" s="5" t="s">
-        <v>3754</v>
-      </c>
       <c r="D379" s="5" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="5" t="s">
+        <v>3754</v>
+      </c>
+      <c r="B380" s="5" t="s">
         <v>3755</v>
       </c>
-      <c r="B380" s="5" t="s">
+      <c r="C380" s="5" t="s">
         <v>3756</v>
       </c>
-      <c r="C380" s="5" t="s">
+      <c r="D380" s="5" t="s">
         <v>3757</v>
-      </c>
-      <c r="D380" s="5" t="s">
-        <v>3758</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="5" t="s">
+        <v>3758</v>
+      </c>
+      <c r="B381" s="5" t="s">
         <v>3759</v>
       </c>
-      <c r="B381" s="5" t="s">
+      <c r="C381" s="5" t="s">
         <v>3760</v>
       </c>
-      <c r="C381" s="5" t="s">
+      <c r="D381" s="5" t="s">
         <v>3761</v>
-      </c>
-      <c r="D381" s="5" t="s">
-        <v>3762</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="5" t="s">
+        <v>3762</v>
+      </c>
+      <c r="B382" s="5" t="s">
         <v>3763</v>
       </c>
-      <c r="B382" s="5" t="s">
+      <c r="C382" s="5" t="s">
         <v>3764</v>
       </c>
-      <c r="C382" s="5" t="s">
-        <v>3765</v>
-      </c>
       <c r="D382" s="5" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="5" t="s">
+        <v>3765</v>
+      </c>
+      <c r="B383" s="5" t="s">
         <v>3766</v>
       </c>
-      <c r="B383" s="5" t="s">
+      <c r="C383" s="5" t="s">
         <v>3767</v>
       </c>
-      <c r="C383" s="5" t="s">
-        <v>3768</v>
-      </c>
       <c r="D383" s="5" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="5" t="s">
+        <v>3768</v>
+      </c>
+      <c r="B384" s="5" t="s">
         <v>3769</v>
       </c>
-      <c r="B384" s="5" t="s">
+      <c r="C384" s="5" t="s">
         <v>3770</v>
       </c>
-      <c r="C384" s="5" t="s">
-        <v>3771</v>
-      </c>
       <c r="D384" s="5" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="5" t="s">
+        <v>3771</v>
+      </c>
+      <c r="B385" s="5" t="s">
         <v>3772</v>
       </c>
-      <c r="B385" s="5" t="s">
+      <c r="C385" s="5" t="s">
         <v>3773</v>
       </c>
-      <c r="C385" s="5" t="s">
-        <v>3774</v>
-      </c>
       <c r="D385" s="5" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="5" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B386" s="5" t="s">
         <v>3775</v>
       </c>
-      <c r="B386" s="5" t="s">
+      <c r="C386" s="5" t="s">
         <v>3776</v>
       </c>
-      <c r="C386" s="5" t="s">
-        <v>3777</v>
-      </c>
       <c r="D386" s="5" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="5" t="s">
+        <v>3777</v>
+      </c>
+      <c r="B387" s="5" t="s">
         <v>3778</v>
-      </c>
-      <c r="B387" s="5" t="s">
-        <v>3779</v>
       </c>
       <c r="C387" s="5" t="s">
         <v>1871</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="5" t="s">
+        <v>3780</v>
+      </c>
+      <c r="B388" s="5" t="s">
         <v>3781</v>
       </c>
-      <c r="B388" s="5" t="s">
+      <c r="C388" s="5" t="s">
         <v>3782</v>
       </c>
-      <c r="C388" s="5" t="s">
+      <c r="D388" s="5" t="s">
         <v>3783</v>
-      </c>
-      <c r="D388" s="5" t="s">
-        <v>3784</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="5" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B389" s="5" t="s">
         <v>3785</v>
       </c>
-      <c r="B389" s="5" t="s">
+      <c r="C389" s="5" t="s">
         <v>3786</v>
       </c>
-      <c r="C389" s="5" t="s">
+      <c r="D389" s="5" t="s">
         <v>3787</v>
-      </c>
-      <c r="D389" s="5" t="s">
-        <v>3788</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="5" t="s">
+        <v>3788</v>
+      </c>
+      <c r="B390" s="5" t="s">
         <v>3789</v>
       </c>
-      <c r="B390" s="5" t="s">
+      <c r="C390" s="5" t="s">
         <v>3790</v>
       </c>
-      <c r="C390" s="5" t="s">
+      <c r="D390" s="5" t="s">
         <v>3791</v>
-      </c>
-      <c r="D390" s="5" t="s">
-        <v>3792</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="5" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B391" s="5" t="s">
         <v>3793</v>
       </c>
-      <c r="B391" s="5" t="s">
+      <c r="C391" s="5" t="s">
         <v>3794</v>
-      </c>
-      <c r="C391" s="5" t="s">
-        <v>3795</v>
       </c>
       <c r="D391" s="5" t="s">
         <v>1991</v>
@@ -31005,10 +31002,10 @@
     </row>
     <row r="392">
       <c r="A392" s="5" t="s">
+        <v>3795</v>
+      </c>
+      <c r="B392" s="5" t="s">
         <v>3796</v>
-      </c>
-      <c r="B392" s="5" t="s">
-        <v>3797</v>
       </c>
       <c r="C392" s="5" t="s">
         <v>1990</v>
@@ -31019,7 +31016,7 @@
     </row>
     <row r="393">
       <c r="A393" s="5" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="B393" s="5" t="s">
         <v>1996</v>
@@ -31033,7 +31030,7 @@
     </row>
     <row r="394">
       <c r="A394" s="5" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="B394" s="5" t="s">
         <v>2002</v>
@@ -31047,7 +31044,7 @@
     </row>
     <row r="395">
       <c r="A395" s="5" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="B395" s="5" t="s">
         <v>2005</v>
@@ -31061,13 +31058,13 @@
     </row>
     <row r="396">
       <c r="A396" s="5" t="s">
+        <v>3800</v>
+      </c>
+      <c r="B396" s="5" t="s">
         <v>3801</v>
       </c>
-      <c r="B396" s="5" t="s">
+      <c r="C396" s="5" t="s">
         <v>3802</v>
-      </c>
-      <c r="C396" s="5" t="s">
-        <v>3803</v>
       </c>
       <c r="D396" s="5" t="s">
         <v>2026</v>
@@ -31075,13 +31072,13 @@
     </row>
     <row r="397">
       <c r="A397" s="5" t="s">
+        <v>3803</v>
+      </c>
+      <c r="B397" s="5" t="s">
         <v>3804</v>
       </c>
-      <c r="B397" s="5" t="s">
+      <c r="C397" s="5" t="s">
         <v>3805</v>
-      </c>
-      <c r="C397" s="5" t="s">
-        <v>3806</v>
       </c>
       <c r="D397" s="5" t="s">
         <v>2026</v>
@@ -31089,13 +31086,13 @@
     </row>
     <row r="398">
       <c r="A398" s="5" t="s">
+        <v>3806</v>
+      </c>
+      <c r="B398" s="5" t="s">
         <v>3807</v>
       </c>
-      <c r="B398" s="5" t="s">
+      <c r="C398" s="5" t="s">
         <v>3808</v>
-      </c>
-      <c r="C398" s="5" t="s">
-        <v>3809</v>
       </c>
       <c r="D398" s="5" t="s">
         <v>2032</v>
@@ -31103,13 +31100,13 @@
     </row>
     <row r="399">
       <c r="A399" s="5" t="s">
+        <v>3809</v>
+      </c>
+      <c r="B399" s="5" t="s">
         <v>3810</v>
       </c>
-      <c r="B399" s="5" t="s">
+      <c r="C399" s="5" t="s">
         <v>3811</v>
-      </c>
-      <c r="C399" s="5" t="s">
-        <v>3812</v>
       </c>
       <c r="D399" s="5" t="s">
         <v>2036</v>
@@ -31117,13 +31114,13 @@
     </row>
     <row r="400">
       <c r="A400" s="5" t="s">
+        <v>3812</v>
+      </c>
+      <c r="B400" s="5" t="s">
         <v>3813</v>
       </c>
-      <c r="B400" s="5" t="s">
+      <c r="C400" s="5" t="s">
         <v>3814</v>
-      </c>
-      <c r="C400" s="5" t="s">
-        <v>3815</v>
       </c>
       <c r="D400" s="5" t="s">
         <v>2036</v>
@@ -31131,13 +31128,13 @@
     </row>
     <row r="401">
       <c r="A401" s="5" t="s">
+        <v>3815</v>
+      </c>
+      <c r="B401" s="5" t="s">
         <v>3816</v>
       </c>
-      <c r="B401" s="5" t="s">
+      <c r="C401" s="5" t="s">
         <v>3817</v>
-      </c>
-      <c r="C401" s="5" t="s">
-        <v>3818</v>
       </c>
       <c r="D401" s="5" t="s">
         <v>2036</v>
@@ -31145,10 +31142,10 @@
     </row>
     <row r="402">
       <c r="A402" s="5" t="s">
+        <v>3818</v>
+      </c>
+      <c r="B402" s="5" t="s">
         <v>3819</v>
-      </c>
-      <c r="B402" s="5" t="s">
-        <v>3820</v>
       </c>
       <c r="C402" s="5" t="s">
         <v>2039</v>
@@ -31159,13 +31156,13 @@
     </row>
     <row r="403">
       <c r="A403" s="5" t="s">
+        <v>3820</v>
+      </c>
+      <c r="B403" s="5" t="s">
         <v>3821</v>
       </c>
-      <c r="B403" s="5" t="s">
+      <c r="C403" s="5" t="s">
         <v>3822</v>
-      </c>
-      <c r="C403" s="5" t="s">
-        <v>3823</v>
       </c>
       <c r="D403" s="5" t="s">
         <v>2036</v>
@@ -31173,13 +31170,13 @@
     </row>
     <row r="404">
       <c r="A404" s="5" t="s">
+        <v>3823</v>
+      </c>
+      <c r="B404" s="5" t="s">
         <v>3824</v>
       </c>
-      <c r="B404" s="5" t="s">
+      <c r="C404" s="5" t="s">
         <v>3825</v>
-      </c>
-      <c r="C404" s="5" t="s">
-        <v>3826</v>
       </c>
       <c r="D404" s="5" t="s">
         <v>2036</v>
@@ -31187,13 +31184,13 @@
     </row>
     <row r="405">
       <c r="A405" s="5" t="s">
+        <v>3826</v>
+      </c>
+      <c r="B405" s="5" t="s">
         <v>3827</v>
       </c>
-      <c r="B405" s="5" t="s">
+      <c r="C405" s="5" t="s">
         <v>3828</v>
-      </c>
-      <c r="C405" s="5" t="s">
-        <v>3829</v>
       </c>
       <c r="D405" s="5" t="s">
         <v>2036</v>
@@ -31201,7 +31198,7 @@
     </row>
     <row r="406">
       <c r="A406" s="5" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="B406" s="5" t="s">
         <v>2044</v>
@@ -31243,13 +31240,13 @@
     </row>
     <row r="409">
       <c r="A409" s="5" t="s">
+        <v>3830</v>
+      </c>
+      <c r="B409" s="5" t="s">
         <v>3831</v>
       </c>
-      <c r="B409" s="5" t="s">
+      <c r="C409" s="5" t="s">
         <v>3832</v>
-      </c>
-      <c r="C409" s="5" t="s">
-        <v>3833</v>
       </c>
       <c r="D409" s="5" t="s">
         <v>2058</v>
@@ -31257,13 +31254,13 @@
     </row>
     <row r="410">
       <c r="A410" s="5" t="s">
+        <v>3833</v>
+      </c>
+      <c r="B410" s="5" t="s">
         <v>3834</v>
       </c>
-      <c r="B410" s="5" t="s">
+      <c r="C410" s="5" t="s">
         <v>3835</v>
-      </c>
-      <c r="C410" s="5" t="s">
-        <v>3836</v>
       </c>
       <c r="D410" s="5" t="s">
         <v>2072</v>
@@ -31271,55 +31268,55 @@
     </row>
     <row r="411">
       <c r="A411" s="5" t="s">
+        <v>3836</v>
+      </c>
+      <c r="B411" s="5" t="s">
         <v>3837</v>
       </c>
-      <c r="B411" s="5" t="s">
+      <c r="C411" s="5" t="s">
         <v>3838</v>
       </c>
-      <c r="C411" s="5" t="s">
+      <c r="D411" s="5" t="s">
         <v>3839</v>
-      </c>
-      <c r="D411" s="5" t="s">
-        <v>3840</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="5" t="s">
+        <v>3840</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>3840</v>
+      </c>
+      <c r="C412" s="5" t="s">
         <v>3841</v>
       </c>
-      <c r="B412" s="5" t="s">
-        <v>3841</v>
-      </c>
-      <c r="C412" s="5" t="s">
-        <v>3842</v>
-      </c>
       <c r="D412" s="5" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="5" t="s">
+        <v>3842</v>
+      </c>
+      <c r="B413" s="5" t="s">
         <v>3843</v>
       </c>
-      <c r="B413" s="5" t="s">
+      <c r="C413" s="5" t="s">
         <v>3844</v>
       </c>
-      <c r="C413" s="5" t="s">
+      <c r="D413" s="5" t="s">
         <v>3845</v>
-      </c>
-      <c r="D413" s="5" t="s">
-        <v>3846</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="5" t="s">
+        <v>3846</v>
+      </c>
+      <c r="B414" s="5" t="s">
         <v>3847</v>
       </c>
-      <c r="B414" s="5" t="s">
+      <c r="C414" s="5" t="s">
         <v>3848</v>
-      </c>
-      <c r="C414" s="5" t="s">
-        <v>3849</v>
       </c>
       <c r="D414" s="5" t="s">
         <v>2079</v>
@@ -31327,7 +31324,7 @@
     </row>
     <row r="415">
       <c r="A415" s="5" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>2081</v>
@@ -31341,13 +31338,13 @@
     </row>
     <row r="416">
       <c r="A416" s="5" t="s">
+        <v>3850</v>
+      </c>
+      <c r="B416" s="5" t="s">
         <v>3851</v>
       </c>
-      <c r="B416" s="5" t="s">
+      <c r="C416" s="5" t="s">
         <v>3852</v>
-      </c>
-      <c r="C416" s="5" t="s">
-        <v>3853</v>
       </c>
       <c r="D416" s="5" t="s">
         <v>2079</v>
@@ -31355,13 +31352,13 @@
     </row>
     <row r="417">
       <c r="A417" s="5" t="s">
+        <v>3853</v>
+      </c>
+      <c r="B417" s="5" t="s">
         <v>3854</v>
       </c>
-      <c r="B417" s="5" t="s">
+      <c r="C417" s="5" t="s">
         <v>3855</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>3856</v>
       </c>
       <c r="D417" s="5" t="s">
         <v>2079</v>
@@ -31369,13 +31366,13 @@
     </row>
     <row r="418">
       <c r="A418" s="5" t="s">
+        <v>3856</v>
+      </c>
+      <c r="B418" s="5" t="s">
         <v>3857</v>
       </c>
-      <c r="B418" s="5" t="s">
+      <c r="C418" s="5" t="s">
         <v>3858</v>
-      </c>
-      <c r="C418" s="5" t="s">
-        <v>3859</v>
       </c>
       <c r="D418" s="5" t="s">
         <v>2086</v>
@@ -31383,7 +31380,7 @@
     </row>
     <row r="419">
       <c r="A419" s="5" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="B419" s="5" t="s">
         <v>2091</v>
@@ -31397,13 +31394,13 @@
     </row>
     <row r="420">
       <c r="A420" s="5" t="s">
+        <v>3860</v>
+      </c>
+      <c r="B420" s="5" t="s">
         <v>3861</v>
       </c>
-      <c r="B420" s="5" t="s">
+      <c r="C420" s="5" t="s">
         <v>3862</v>
-      </c>
-      <c r="C420" s="5" t="s">
-        <v>3863</v>
       </c>
       <c r="D420" s="5" t="s">
         <v>2086</v>
@@ -31411,13 +31408,13 @@
     </row>
     <row r="421">
       <c r="A421" s="5" t="s">
+        <v>3863</v>
+      </c>
+      <c r="B421" s="5" t="s">
         <v>3864</v>
       </c>
-      <c r="B421" s="5" t="s">
+      <c r="C421" s="5" t="s">
         <v>3865</v>
-      </c>
-      <c r="C421" s="5" t="s">
-        <v>3866</v>
       </c>
       <c r="D421" s="5" t="s">
         <v>2086</v>
@@ -31425,13 +31422,13 @@
     </row>
     <row r="422">
       <c r="A422" s="5" t="s">
+        <v>3866</v>
+      </c>
+      <c r="B422" s="5" t="s">
         <v>3867</v>
       </c>
-      <c r="B422" s="5" t="s">
+      <c r="C422" s="5" t="s">
         <v>3868</v>
-      </c>
-      <c r="C422" s="5" t="s">
-        <v>3869</v>
       </c>
       <c r="D422" s="5" t="s">
         <v>2086</v>
@@ -31439,13 +31436,13 @@
     </row>
     <row r="423">
       <c r="A423" s="5" t="s">
+        <v>3869</v>
+      </c>
+      <c r="B423" s="5" t="s">
         <v>3870</v>
       </c>
-      <c r="B423" s="5" t="s">
+      <c r="C423" s="5" t="s">
         <v>3871</v>
-      </c>
-      <c r="C423" s="5" t="s">
-        <v>3872</v>
       </c>
       <c r="D423" s="5" t="s">
         <v>2086</v>
@@ -31453,13 +31450,13 @@
     </row>
     <row r="424">
       <c r="A424" s="5" t="s">
+        <v>3872</v>
+      </c>
+      <c r="B424" s="5" t="s">
         <v>3873</v>
       </c>
-      <c r="B424" s="5" t="s">
+      <c r="C424" s="5" t="s">
         <v>3874</v>
-      </c>
-      <c r="C424" s="5" t="s">
-        <v>3875</v>
       </c>
       <c r="D424" s="5" t="s">
         <v>2086</v>
@@ -31467,13 +31464,13 @@
     </row>
     <row r="425">
       <c r="A425" s="5" t="s">
+        <v>3875</v>
+      </c>
+      <c r="B425" s="5" t="s">
         <v>3876</v>
       </c>
-      <c r="B425" s="5" t="s">
+      <c r="C425" s="5" t="s">
         <v>3877</v>
-      </c>
-      <c r="C425" s="5" t="s">
-        <v>3878</v>
       </c>
       <c r="D425" s="5" t="s">
         <v>2086</v>
@@ -31481,13 +31478,13 @@
     </row>
     <row r="426">
       <c r="A426" s="5" t="s">
+        <v>3878</v>
+      </c>
+      <c r="B426" s="5" t="s">
         <v>3879</v>
       </c>
-      <c r="B426" s="5" t="s">
+      <c r="C426" s="5" t="s">
         <v>3880</v>
-      </c>
-      <c r="C426" s="5" t="s">
-        <v>3881</v>
       </c>
       <c r="D426" s="5" t="s">
         <v>2099</v>
@@ -31495,13 +31492,13 @@
     </row>
     <row r="427">
       <c r="A427" s="5" t="s">
+        <v>3881</v>
+      </c>
+      <c r="B427" s="5" t="s">
         <v>3882</v>
       </c>
-      <c r="B427" s="5" t="s">
+      <c r="C427" s="5" t="s">
         <v>3883</v>
-      </c>
-      <c r="C427" s="5" t="s">
-        <v>3884</v>
       </c>
       <c r="D427" s="5" t="s">
         <v>2123</v>
@@ -31509,13 +31506,13 @@
     </row>
     <row r="428">
       <c r="A428" s="5" t="s">
+        <v>3884</v>
+      </c>
+      <c r="B428" s="5" t="s">
         <v>3885</v>
       </c>
-      <c r="B428" s="5" t="s">
+      <c r="C428" s="5" t="s">
         <v>3886</v>
-      </c>
-      <c r="C428" s="5" t="s">
-        <v>3887</v>
       </c>
       <c r="D428" s="5" t="s">
         <v>2143</v>
@@ -31523,10 +31520,10 @@
     </row>
     <row r="429">
       <c r="A429" s="5" t="s">
+        <v>3887</v>
+      </c>
+      <c r="B429" s="5" t="s">
         <v>3888</v>
-      </c>
-      <c r="B429" s="5" t="s">
-        <v>3889</v>
       </c>
       <c r="C429" s="5" t="s">
         <v>2152</v>
@@ -31551,7 +31548,7 @@
     </row>
     <row r="431">
       <c r="A431" s="5" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="B431" s="5" t="s">
         <v>2181</v>
@@ -31565,7 +31562,7 @@
     </row>
     <row r="432">
       <c r="A432" s="5" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="B432" s="5" t="s">
         <v>2185</v>
@@ -31579,7 +31576,7 @@
     </row>
     <row r="433">
       <c r="A433" s="5" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="B433" s="5" t="s">
         <v>2189</v>
@@ -31593,7 +31590,7 @@
     </row>
     <row r="434">
       <c r="A434" s="5" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>2192</v>
@@ -31607,10 +31604,10 @@
     </row>
     <row r="435">
       <c r="A435" s="5" t="s">
+        <v>3893</v>
+      </c>
+      <c r="B435" s="5" t="s">
         <v>3894</v>
-      </c>
-      <c r="B435" s="5" t="s">
-        <v>3895</v>
       </c>
       <c r="C435" s="5" t="s">
         <v>2196</v>
@@ -31621,13 +31618,13 @@
     </row>
     <row r="436">
       <c r="A436" s="5" t="s">
+        <v>3895</v>
+      </c>
+      <c r="B436" s="5" t="s">
         <v>3896</v>
       </c>
-      <c r="B436" s="5" t="s">
+      <c r="C436" s="5" t="s">
         <v>3897</v>
-      </c>
-      <c r="C436" s="5" t="s">
-        <v>3898</v>
       </c>
       <c r="D436" s="5" t="s">
         <v>2200</v>
@@ -31635,13 +31632,13 @@
     </row>
     <row r="437">
       <c r="A437" s="5" t="s">
+        <v>3898</v>
+      </c>
+      <c r="B437" s="5" t="s">
         <v>3899</v>
       </c>
-      <c r="B437" s="5" t="s">
+      <c r="C437" s="5" t="s">
         <v>3900</v>
-      </c>
-      <c r="C437" s="5" t="s">
-        <v>3901</v>
       </c>
       <c r="D437" s="5" t="s">
         <v>2200</v>
@@ -31649,13 +31646,13 @@
     </row>
     <row r="438">
       <c r="A438" s="5" t="s">
+        <v>3901</v>
+      </c>
+      <c r="B438" s="5" t="s">
         <v>3902</v>
       </c>
-      <c r="B438" s="5" t="s">
+      <c r="C438" s="5" t="s">
         <v>3903</v>
-      </c>
-      <c r="C438" s="5" t="s">
-        <v>3904</v>
       </c>
       <c r="D438" s="5" t="s">
         <v>2200</v>
@@ -31663,7 +31660,7 @@
     </row>
     <row r="439">
       <c r="A439" s="5" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="B439" s="5" t="s">
         <v>2209</v>
@@ -31677,7 +31674,7 @@
     </row>
     <row r="440">
       <c r="A440" s="5" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>2218</v>
@@ -31691,66 +31688,66 @@
     </row>
     <row r="441">
       <c r="A441" s="5" t="s">
+        <v>3906</v>
+      </c>
+      <c r="B441" s="5" t="s">
         <v>3907</v>
-      </c>
-      <c r="B441" s="5" t="s">
-        <v>3908</v>
       </c>
       <c r="C441" s="5" t="s">
         <v>1591</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="5" t="s">
+        <v>3909</v>
+      </c>
+      <c r="B442" s="5" t="s">
         <v>3910</v>
-      </c>
-      <c r="B442" s="5" t="s">
-        <v>3911</v>
       </c>
       <c r="C442" s="5" t="s">
         <v>1606</v>
       </c>
       <c r="D442" s="5" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="5" t="s">
+        <v>3911</v>
+      </c>
+      <c r="B443" s="5" t="s">
         <v>3912</v>
-      </c>
-      <c r="B443" s="5" t="s">
-        <v>3913</v>
       </c>
       <c r="C443" s="5" t="s">
         <v>1639</v>
       </c>
       <c r="D443" s="5" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="5" t="s">
+        <v>3913</v>
+      </c>
+      <c r="B444" s="5" t="s">
         <v>3914</v>
-      </c>
-      <c r="B444" s="5" t="s">
-        <v>3915</v>
       </c>
       <c r="C444" s="5" t="s">
         <v>1645</v>
       </c>
       <c r="D444" s="5" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="5" t="s">
+        <v>3915</v>
+      </c>
+      <c r="B445" s="5" t="s">
         <v>3916</v>
-      </c>
-      <c r="B445" s="5" t="s">
-        <v>3917</v>
       </c>
       <c r="C445" s="5" t="s">
         <v>1375</v>
@@ -31761,7 +31758,7 @@
     </row>
     <row r="446">
       <c r="A446" s="5" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>2280</v>
@@ -31789,10 +31786,10 @@
     </row>
     <row r="448">
       <c r="A448" s="5" t="s">
+        <v>3918</v>
+      </c>
+      <c r="B448" s="5" t="s">
         <v>3919</v>
-      </c>
-      <c r="B448" s="5" t="s">
-        <v>3920</v>
       </c>
       <c r="C448" s="5" t="s">
         <v>2318</v>
@@ -31803,7 +31800,7 @@
     </row>
     <row r="449">
       <c r="A449" s="5" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="B449" s="5" t="s">
         <v>2321</v>
@@ -31817,13 +31814,13 @@
     </row>
     <row r="450">
       <c r="A450" s="5" t="s">
+        <v>3921</v>
+      </c>
+      <c r="B450" s="5" t="s">
         <v>3922</v>
       </c>
-      <c r="B450" s="5" t="s">
+      <c r="C450" s="5" t="s">
         <v>3923</v>
-      </c>
-      <c r="C450" s="5" t="s">
-        <v>3924</v>
       </c>
       <c r="D450" s="5" t="s">
         <v>2323</v>
@@ -31831,13 +31828,13 @@
     </row>
     <row r="451">
       <c r="A451" s="5" t="s">
+        <v>3924</v>
+      </c>
+      <c r="B451" s="5" t="s">
         <v>3925</v>
       </c>
-      <c r="B451" s="5" t="s">
+      <c r="C451" s="5" t="s">
         <v>3926</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>3927</v>
       </c>
       <c r="D451" s="5" t="s">
         <v>2323</v>
@@ -31845,7 +31842,7 @@
     </row>
     <row r="452">
       <c r="A452" s="5" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>2332</v>
@@ -31859,13 +31856,13 @@
     </row>
     <row r="453">
       <c r="A453" s="5" t="s">
+        <v>3928</v>
+      </c>
+      <c r="B453" s="5" t="s">
         <v>3929</v>
       </c>
-      <c r="B453" s="5" t="s">
+      <c r="C453" s="5" t="s">
         <v>3930</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>3931</v>
       </c>
       <c r="D453" s="5" t="s">
         <v>2327</v>
@@ -31873,7 +31870,7 @@
     </row>
     <row r="454">
       <c r="A454" s="5" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="B454" s="5" t="s">
         <v>2338</v>
@@ -31887,7 +31884,7 @@
     </row>
     <row r="455">
       <c r="A455" s="5" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="B455" s="5" t="s">
         <v>2341</v>
@@ -31901,7 +31898,7 @@
     </row>
     <row r="456">
       <c r="A456" s="5" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="B456" s="5" t="s">
         <v>2344</v>
@@ -31915,13 +31912,13 @@
     </row>
     <row r="457">
       <c r="A457" s="5" t="s">
+        <v>3934</v>
+      </c>
+      <c r="B457" s="5" t="s">
         <v>3935</v>
       </c>
-      <c r="B457" s="5" t="s">
+      <c r="C457" s="5" t="s">
         <v>3936</v>
-      </c>
-      <c r="C457" s="5" t="s">
-        <v>3937</v>
       </c>
       <c r="D457" s="5" t="s">
         <v>2327</v>
@@ -31929,13 +31926,13 @@
     </row>
     <row r="458">
       <c r="A458" s="5" t="s">
+        <v>3937</v>
+      </c>
+      <c r="B458" s="5" t="s">
         <v>3938</v>
       </c>
-      <c r="B458" s="5" t="s">
+      <c r="C458" s="5" t="s">
         <v>3939</v>
-      </c>
-      <c r="C458" s="5" t="s">
-        <v>3940</v>
       </c>
       <c r="D458" s="5" t="s">
         <v>2327</v>
@@ -31943,7 +31940,7 @@
     </row>
     <row r="459">
       <c r="A459" s="5" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="B459" s="5" t="s">
         <v>2347</v>
@@ -31957,27 +31954,27 @@
     </row>
     <row r="460">
       <c r="A460" s="5" t="s">
+        <v>3941</v>
+      </c>
+      <c r="B460" s="5" t="s">
         <v>3942</v>
       </c>
-      <c r="B460" s="5" t="s">
+      <c r="C460" s="5" t="s">
         <v>3943</v>
       </c>
-      <c r="C460" s="5" t="s">
+      <c r="D460" s="5" t="s">
         <v>3944</v>
-      </c>
-      <c r="D460" s="5" t="s">
-        <v>3945</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="5" t="s">
+        <v>3945</v>
+      </c>
+      <c r="B461" s="5" t="s">
         <v>3946</v>
       </c>
-      <c r="B461" s="5" t="s">
+      <c r="C461" s="5" t="s">
         <v>3947</v>
-      </c>
-      <c r="C461" s="5" t="s">
-        <v>3948</v>
       </c>
       <c r="D461" s="5" t="s">
         <v>2362</v>
@@ -31985,13 +31982,13 @@
     </row>
     <row r="462">
       <c r="A462" s="5" t="s">
+        <v>3948</v>
+      </c>
+      <c r="B462" s="5" t="s">
         <v>3949</v>
       </c>
-      <c r="B462" s="5" t="s">
+      <c r="C462" s="5" t="s">
         <v>3950</v>
-      </c>
-      <c r="C462" s="5" t="s">
-        <v>3951</v>
       </c>
       <c r="D462" s="5" t="s">
         <v>2362</v>
@@ -31999,13 +31996,13 @@
     </row>
     <row r="463">
       <c r="A463" s="5" t="s">
+        <v>3951</v>
+      </c>
+      <c r="B463" s="5" t="s">
         <v>3952</v>
       </c>
-      <c r="B463" s="5" t="s">
+      <c r="C463" s="5" t="s">
         <v>3953</v>
-      </c>
-      <c r="C463" s="5" t="s">
-        <v>3954</v>
       </c>
       <c r="D463" s="5" t="s">
         <v>2362</v>
@@ -32013,7 +32010,7 @@
     </row>
     <row r="464">
       <c r="A464" s="5" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="B464" s="5" t="s">
         <v>2374</v>
@@ -32027,7 +32024,7 @@
     </row>
     <row r="465">
       <c r="A465" s="5" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="B465" s="5" t="s">
         <v>2377</v>
@@ -32041,7 +32038,7 @@
     </row>
     <row r="466">
       <c r="A466" s="5" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="B466" s="5" t="s">
         <v>2383</v>
@@ -32055,7 +32052,7 @@
     </row>
     <row r="467">
       <c r="A467" s="5" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="B467" s="5" t="s">
         <v>2386</v>
@@ -32069,7 +32066,7 @@
     </row>
     <row r="468">
       <c r="A468" s="5" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="B468" s="5" t="s">
         <v>2389</v>
@@ -32083,7 +32080,7 @@
     </row>
     <row r="469">
       <c r="A469" s="5" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="B469" s="5" t="s">
         <v>2395</v>
@@ -32097,13 +32094,13 @@
     </row>
     <row r="470">
       <c r="A470" s="5" t="s">
+        <v>3960</v>
+      </c>
+      <c r="B470" s="5" t="s">
         <v>3961</v>
       </c>
-      <c r="B470" s="5" t="s">
+      <c r="C470" s="5" t="s">
         <v>3962</v>
-      </c>
-      <c r="C470" s="5" t="s">
-        <v>3963</v>
       </c>
       <c r="D470" s="5" t="s">
         <v>2372</v>
@@ -32111,7 +32108,7 @@
     </row>
     <row r="471">
       <c r="A471" s="5" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="B471" s="5" t="s">
         <v>2401</v>
@@ -32125,7 +32122,7 @@
     </row>
     <row r="472">
       <c r="A472" s="5" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="B472" s="5" t="s">
         <v>2407</v>
@@ -32139,7 +32136,7 @@
     </row>
     <row r="473">
       <c r="A473" s="5" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="B473" s="5" t="s">
         <v>2410</v>
@@ -32153,7 +32150,7 @@
     </row>
     <row r="474">
       <c r="A474" s="5" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="B474" s="5" t="s">
         <v>2413</v>
@@ -32167,7 +32164,7 @@
     </row>
     <row r="475">
       <c r="A475" s="5" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="B475" s="5" t="s">
         <v>2419</v>
@@ -32181,7 +32178,7 @@
     </row>
     <row r="476">
       <c r="A476" s="5" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="B476" s="5" t="s">
         <v>2422</v>
@@ -32195,7 +32192,7 @@
     </row>
     <row r="477">
       <c r="A477" s="5" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="B477" s="5" t="s">
         <v>2428</v>
@@ -32209,13 +32206,13 @@
     </row>
     <row r="478">
       <c r="A478" s="5" t="s">
+        <v>3970</v>
+      </c>
+      <c r="B478" s="5" t="s">
         <v>3971</v>
       </c>
-      <c r="B478" s="5" t="s">
+      <c r="C478" s="5" t="s">
         <v>3972</v>
-      </c>
-      <c r="C478" s="5" t="s">
-        <v>3973</v>
       </c>
       <c r="D478" s="5" t="s">
         <v>2433</v>
@@ -32223,13 +32220,13 @@
     </row>
     <row r="479">
       <c r="A479" s="5" t="s">
+        <v>3973</v>
+      </c>
+      <c r="B479" s="5" t="s">
         <v>3974</v>
       </c>
-      <c r="B479" s="5" t="s">
+      <c r="C479" s="5" t="s">
         <v>3975</v>
-      </c>
-      <c r="C479" s="5" t="s">
-        <v>3976</v>
       </c>
       <c r="D479" s="5" t="s">
         <v>2440</v>
@@ -32237,13 +32234,13 @@
     </row>
     <row r="480">
       <c r="A480" s="5" t="s">
+        <v>3976</v>
+      </c>
+      <c r="B480" s="5" t="s">
         <v>3977</v>
       </c>
-      <c r="B480" s="5" t="s">
+      <c r="C480" s="5" t="s">
         <v>3978</v>
-      </c>
-      <c r="C480" s="5" t="s">
-        <v>3979</v>
       </c>
       <c r="D480" s="5" t="s">
         <v>2440</v>
@@ -32251,13 +32248,13 @@
     </row>
     <row r="481">
       <c r="A481" s="5" t="s">
+        <v>3979</v>
+      </c>
+      <c r="B481" s="5" t="s">
         <v>3980</v>
       </c>
-      <c r="B481" s="5" t="s">
+      <c r="C481" s="5" t="s">
         <v>3981</v>
-      </c>
-      <c r="C481" s="5" t="s">
-        <v>3982</v>
       </c>
       <c r="D481" s="5" t="s">
         <v>2440</v>
@@ -32265,13 +32262,13 @@
     </row>
     <row r="482">
       <c r="A482" s="5" t="s">
+        <v>3982</v>
+      </c>
+      <c r="B482" s="5" t="s">
         <v>3983</v>
       </c>
-      <c r="B482" s="5" t="s">
+      <c r="C482" s="5" t="s">
         <v>3984</v>
-      </c>
-      <c r="C482" s="5" t="s">
-        <v>3985</v>
       </c>
       <c r="D482" s="5" t="s">
         <v>2440</v>
@@ -32279,13 +32276,13 @@
     </row>
     <row r="483">
       <c r="A483" s="5" t="s">
+        <v>3985</v>
+      </c>
+      <c r="B483" s="5" t="s">
         <v>3986</v>
       </c>
-      <c r="B483" s="5" t="s">
+      <c r="C483" s="5" t="s">
         <v>3987</v>
-      </c>
-      <c r="C483" s="5" t="s">
-        <v>3988</v>
       </c>
       <c r="D483" s="5" t="s">
         <v>2440</v>
@@ -32293,13 +32290,13 @@
     </row>
     <row r="484">
       <c r="A484" s="5" t="s">
+        <v>3988</v>
+      </c>
+      <c r="B484" s="5" t="s">
         <v>3989</v>
       </c>
-      <c r="B484" s="5" t="s">
+      <c r="C484" s="5" t="s">
         <v>3990</v>
-      </c>
-      <c r="C484" s="5" t="s">
-        <v>3991</v>
       </c>
       <c r="D484" s="5" t="s">
         <v>2440</v>
@@ -32307,13 +32304,13 @@
     </row>
     <row r="485">
       <c r="A485" s="5" t="s">
+        <v>3991</v>
+      </c>
+      <c r="B485" s="5" t="s">
         <v>3992</v>
       </c>
-      <c r="B485" s="5" t="s">
+      <c r="C485" s="5" t="s">
         <v>3993</v>
-      </c>
-      <c r="C485" s="5" t="s">
-        <v>3994</v>
       </c>
       <c r="D485" s="5" t="s">
         <v>2440</v>
@@ -32321,13 +32318,13 @@
     </row>
     <row r="486">
       <c r="A486" s="5" t="s">
+        <v>3994</v>
+      </c>
+      <c r="B486" s="5" t="s">
         <v>3995</v>
       </c>
-      <c r="B486" s="5" t="s">
+      <c r="C486" s="5" t="s">
         <v>3996</v>
-      </c>
-      <c r="C486" s="5" t="s">
-        <v>3997</v>
       </c>
       <c r="D486" s="5" t="s">
         <v>2440</v>
@@ -32335,13 +32332,13 @@
     </row>
     <row r="487">
       <c r="A487" s="5" t="s">
+        <v>3997</v>
+      </c>
+      <c r="B487" s="5" t="s">
         <v>3998</v>
       </c>
-      <c r="B487" s="5" t="s">
+      <c r="C487" s="5" t="s">
         <v>3999</v>
-      </c>
-      <c r="C487" s="5" t="s">
-        <v>4000</v>
       </c>
       <c r="D487" s="5" t="s">
         <v>2440</v>
@@ -32349,13 +32346,13 @@
     </row>
     <row r="488">
       <c r="A488" s="5" t="s">
+        <v>4000</v>
+      </c>
+      <c r="B488" s="5" t="s">
         <v>4001</v>
       </c>
-      <c r="B488" s="5" t="s">
+      <c r="C488" s="5" t="s">
         <v>4002</v>
-      </c>
-      <c r="C488" s="5" t="s">
-        <v>4003</v>
       </c>
       <c r="D488" s="5" t="s">
         <v>2481</v>
@@ -32363,13 +32360,13 @@
     </row>
     <row r="489">
       <c r="A489" s="5" t="s">
+        <v>4003</v>
+      </c>
+      <c r="B489" s="5" t="s">
         <v>4004</v>
       </c>
-      <c r="B489" s="5" t="s">
+      <c r="C489" s="5" t="s">
         <v>4005</v>
-      </c>
-      <c r="C489" s="5" t="s">
-        <v>4006</v>
       </c>
       <c r="D489" s="5" t="s">
         <v>2481</v>
@@ -32377,13 +32374,13 @@
     </row>
     <row r="490">
       <c r="A490" s="5" t="s">
+        <v>4006</v>
+      </c>
+      <c r="B490" s="5" t="s">
         <v>4007</v>
       </c>
-      <c r="B490" s="5" t="s">
+      <c r="C490" s="5" t="s">
         <v>4008</v>
-      </c>
-      <c r="C490" s="5" t="s">
-        <v>4009</v>
       </c>
       <c r="D490" s="5" t="s">
         <v>2481</v>
@@ -32391,13 +32388,13 @@
     </row>
     <row r="491">
       <c r="A491" s="5" t="s">
+        <v>4009</v>
+      </c>
+      <c r="B491" s="5" t="s">
         <v>4010</v>
       </c>
-      <c r="B491" s="5" t="s">
+      <c r="C491" s="5" t="s">
         <v>4011</v>
-      </c>
-      <c r="C491" s="5" t="s">
-        <v>4012</v>
       </c>
       <c r="D491" s="5" t="s">
         <v>2481</v>
@@ -32405,13 +32402,13 @@
     </row>
     <row r="492">
       <c r="A492" s="5" t="s">
+        <v>4012</v>
+      </c>
+      <c r="B492" s="5" t="s">
         <v>4013</v>
       </c>
-      <c r="B492" s="5" t="s">
+      <c r="C492" s="5" t="s">
         <v>4014</v>
-      </c>
-      <c r="C492" s="5" t="s">
-        <v>4015</v>
       </c>
       <c r="D492" s="5" t="s">
         <v>2481</v>
@@ -32419,13 +32416,13 @@
     </row>
     <row r="493">
       <c r="A493" s="5" t="s">
+        <v>4015</v>
+      </c>
+      <c r="B493" s="5" t="s">
         <v>4016</v>
       </c>
-      <c r="B493" s="5" t="s">
+      <c r="C493" s="5" t="s">
         <v>4017</v>
-      </c>
-      <c r="C493" s="5" t="s">
-        <v>4018</v>
       </c>
       <c r="D493" s="5" t="s">
         <v>2481</v>
@@ -32433,13 +32430,13 @@
     </row>
     <row r="494">
       <c r="A494" s="5" t="s">
+        <v>4018</v>
+      </c>
+      <c r="B494" s="5" t="s">
         <v>4019</v>
       </c>
-      <c r="B494" s="5" t="s">
+      <c r="C494" s="5" t="s">
         <v>4020</v>
-      </c>
-      <c r="C494" s="5" t="s">
-        <v>4021</v>
       </c>
       <c r="D494" s="5" t="s">
         <v>2481</v>
@@ -32447,13 +32444,13 @@
     </row>
     <row r="495">
       <c r="A495" s="5" t="s">
+        <v>4021</v>
+      </c>
+      <c r="B495" s="5" t="s">
         <v>4022</v>
       </c>
-      <c r="B495" s="5" t="s">
+      <c r="C495" s="5" t="s">
         <v>4023</v>
-      </c>
-      <c r="C495" s="5" t="s">
-        <v>4024</v>
       </c>
       <c r="D495" s="5" t="s">
         <v>2481</v>
@@ -32461,35 +32458,35 @@
     </row>
     <row r="496">
       <c r="A496" s="5" t="s">
+        <v>4024</v>
+      </c>
+      <c r="B496" s="5" t="s">
         <v>4025</v>
       </c>
-      <c r="B496" s="5" t="s">
+      <c r="C496" s="5" t="s">
         <v>4026</v>
       </c>
-      <c r="C496" s="5" t="s">
+      <c r="D496" s="5" t="s">
         <v>4027</v>
-      </c>
-      <c r="D496" s="5" t="s">
-        <v>4028</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="5" t="s">
+        <v>4028</v>
+      </c>
+      <c r="B497" s="5" t="s">
         <v>4029</v>
       </c>
-      <c r="B497" s="5" t="s">
+      <c r="C497" s="5" t="s">
         <v>4030</v>
       </c>
-      <c r="C497" s="5" t="s">
-        <v>4031</v>
-      </c>
       <c r="D497" s="5" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="5" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="B498" s="5" t="s">
         <v>2500</v>
@@ -32503,7 +32500,7 @@
     </row>
     <row r="499">
       <c r="A499" s="5" t="s">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="B499" s="5" t="s">
         <v>2520</v>
@@ -32517,63 +32514,63 @@
     </row>
     <row r="500">
       <c r="A500" s="5" t="s">
+        <v>4033</v>
+      </c>
+      <c r="B500" s="5" t="s">
         <v>4034</v>
-      </c>
-      <c r="B500" s="5" t="s">
-        <v>4035</v>
       </c>
       <c r="C500" s="5" t="s">
         <v>562</v>
       </c>
       <c r="D500" s="5" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="5" t="s">
+        <v>4036</v>
+      </c>
+      <c r="B501" s="5" t="s">
         <v>4037</v>
       </c>
-      <c r="B501" s="5" t="s">
+      <c r="C501" s="5" t="s">
         <v>4038</v>
       </c>
-      <c r="C501" s="5" t="s">
-        <v>4039</v>
-      </c>
       <c r="D501" s="5" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="5" t="s">
+        <v>4039</v>
+      </c>
+      <c r="B502" s="5" t="s">
+        <v>4039</v>
+      </c>
+      <c r="C502" s="5" t="s">
         <v>4040</v>
       </c>
-      <c r="B502" s="5" t="s">
-        <v>4040</v>
-      </c>
-      <c r="C502" s="5" t="s">
-        <v>4041</v>
-      </c>
       <c r="D502" s="5" t="s">
-        <v>4040</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="5" t="s">
+        <v>4041</v>
+      </c>
+      <c r="B503" s="5" t="s">
         <v>4042</v>
       </c>
-      <c r="B503" s="5" t="s">
+      <c r="C503" s="5" t="s">
         <v>4043</v>
       </c>
-      <c r="C503" s="5" t="s">
+      <c r="D503" s="5" t="s">
         <v>4044</v>
-      </c>
-      <c r="D503" s="5" t="s">
-        <v>4045</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="5" t="s">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="B504" s="5" t="s">
         <v>2534</v>
@@ -32587,13 +32584,13 @@
     </row>
     <row r="505">
       <c r="A505" s="5" t="s">
+        <v>4046</v>
+      </c>
+      <c r="B505" s="5" t="s">
         <v>4047</v>
       </c>
-      <c r="B505" s="5" t="s">
+      <c r="C505" s="5" t="s">
         <v>4048</v>
-      </c>
-      <c r="C505" s="5" t="s">
-        <v>4049</v>
       </c>
       <c r="D505" s="5" t="s">
         <v>2536</v>
@@ -32601,7 +32598,7 @@
     </row>
     <row r="506">
       <c r="A506" s="5" t="s">
-        <v>4050</v>
+        <v>4049</v>
       </c>
       <c r="B506" s="5" t="s">
         <v>2541</v>
@@ -32615,7 +32612,7 @@
     </row>
     <row r="507">
       <c r="A507" s="5" t="s">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="B507" s="5" t="s">
         <v>2544</v>
@@ -32629,7 +32626,7 @@
     </row>
     <row r="508">
       <c r="A508" s="5" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="B508" s="5" t="s">
         <v>2569</v>
@@ -32643,13 +32640,13 @@
     </row>
     <row r="509">
       <c r="A509" s="5" t="s">
+        <v>4052</v>
+      </c>
+      <c r="B509" s="5" t="s">
         <v>4053</v>
       </c>
-      <c r="B509" s="5" t="s">
+      <c r="C509" s="5" t="s">
         <v>4054</v>
-      </c>
-      <c r="C509" s="5" t="s">
-        <v>4055</v>
       </c>
       <c r="D509" s="5" t="s">
         <v>2564</v>
@@ -32657,10 +32654,10 @@
     </row>
     <row r="510">
       <c r="A510" s="5" t="s">
+        <v>4055</v>
+      </c>
+      <c r="B510" s="5" t="s">
         <v>4056</v>
-      </c>
-      <c r="B510" s="5" t="s">
-        <v>4057</v>
       </c>
       <c r="C510" s="5" t="s">
         <v>2573</v>
@@ -32671,7 +32668,7 @@
     </row>
     <row r="511">
       <c r="A511" s="5" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="B511" s="5" t="s">
         <v>2578</v>
@@ -32699,27 +32696,27 @@
     </row>
     <row r="513">
       <c r="A513" s="5" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B513" s="5" t="s">
+        <v>4058</v>
+      </c>
+      <c r="C513" s="5" t="s">
         <v>4059</v>
       </c>
-      <c r="B513" s="5" t="s">
-        <v>4059</v>
-      </c>
-      <c r="C513" s="5" t="s">
-        <v>4060</v>
-      </c>
       <c r="D513" s="5" t="s">
-        <v>4059</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="5" t="s">
+        <v>4060</v>
+      </c>
+      <c r="B514" s="5" t="s">
         <v>4061</v>
       </c>
-      <c r="B514" s="5" t="s">
+      <c r="C514" s="5" t="s">
         <v>4062</v>
-      </c>
-      <c r="C514" s="5" t="s">
-        <v>4063</v>
       </c>
       <c r="D514" s="5" t="s">
         <v>2586</v>
@@ -32727,13 +32724,13 @@
     </row>
     <row r="515">
       <c r="A515" s="5" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B515" s="5" t="s">
         <v>4064</v>
       </c>
-      <c r="B515" s="5" t="s">
+      <c r="C515" s="5" t="s">
         <v>4065</v>
-      </c>
-      <c r="C515" s="5" t="s">
-        <v>4066</v>
       </c>
       <c r="D515" s="5" t="s">
         <v>2586</v>
@@ -32741,13 +32738,13 @@
     </row>
     <row r="516">
       <c r="A516" s="5" t="s">
+        <v>4066</v>
+      </c>
+      <c r="B516" s="5" t="s">
         <v>4067</v>
       </c>
-      <c r="B516" s="5" t="s">
+      <c r="C516" s="5" t="s">
         <v>4068</v>
-      </c>
-      <c r="C516" s="5" t="s">
-        <v>4069</v>
       </c>
       <c r="D516" s="5" t="s">
         <v>2586</v>
@@ -32755,13 +32752,13 @@
     </row>
     <row r="517">
       <c r="A517" s="5" t="s">
+        <v>4069</v>
+      </c>
+      <c r="B517" s="5" t="s">
         <v>4070</v>
       </c>
-      <c r="B517" s="5" t="s">
+      <c r="C517" s="5" t="s">
         <v>4071</v>
-      </c>
-      <c r="C517" s="5" t="s">
-        <v>4072</v>
       </c>
       <c r="D517" s="5" t="s">
         <v>2586</v>
@@ -32769,13 +32766,13 @@
     </row>
     <row r="518">
       <c r="A518" s="5" t="s">
+        <v>4072</v>
+      </c>
+      <c r="B518" s="5" t="s">
         <v>4073</v>
       </c>
-      <c r="B518" s="5" t="s">
+      <c r="C518" s="5" t="s">
         <v>4074</v>
-      </c>
-      <c r="C518" s="5" t="s">
-        <v>4075</v>
       </c>
       <c r="D518" s="5" t="s">
         <v>2586</v>
@@ -32783,13 +32780,13 @@
     </row>
     <row r="519">
       <c r="A519" s="5" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B519" s="5" t="s">
         <v>4076</v>
       </c>
-      <c r="B519" s="5" t="s">
+      <c r="C519" s="5" t="s">
         <v>4077</v>
-      </c>
-      <c r="C519" s="5" t="s">
-        <v>4078</v>
       </c>
       <c r="D519" s="5" t="s">
         <v>2586</v>
@@ -32797,13 +32794,13 @@
     </row>
     <row r="520">
       <c r="A520" s="5" t="s">
+        <v>4078</v>
+      </c>
+      <c r="B520" s="5" t="s">
         <v>4079</v>
       </c>
-      <c r="B520" s="5" t="s">
+      <c r="C520" s="5" t="s">
         <v>4080</v>
-      </c>
-      <c r="C520" s="5" t="s">
-        <v>4081</v>
       </c>
       <c r="D520" s="5" t="s">
         <v>2586</v>
@@ -32811,13 +32808,13 @@
     </row>
     <row r="521">
       <c r="A521" s="5" t="s">
+        <v>4081</v>
+      </c>
+      <c r="B521" s="5" t="s">
         <v>4082</v>
       </c>
-      <c r="B521" s="5" t="s">
+      <c r="C521" s="5" t="s">
         <v>4083</v>
-      </c>
-      <c r="C521" s="5" t="s">
-        <v>4084</v>
       </c>
       <c r="D521" s="5" t="s">
         <v>2586</v>
@@ -32825,13 +32822,13 @@
     </row>
     <row r="522">
       <c r="A522" s="5" t="s">
+        <v>4084</v>
+      </c>
+      <c r="B522" s="5" t="s">
         <v>4085</v>
       </c>
-      <c r="B522" s="5" t="s">
+      <c r="C522" s="5" t="s">
         <v>4086</v>
-      </c>
-      <c r="C522" s="5" t="s">
-        <v>4087</v>
       </c>
       <c r="D522" s="5" t="s">
         <v>2586</v>
@@ -32839,13 +32836,13 @@
     </row>
     <row r="523">
       <c r="A523" s="5" t="s">
+        <v>4087</v>
+      </c>
+      <c r="B523" s="5" t="s">
         <v>4088</v>
       </c>
-      <c r="B523" s="5" t="s">
+      <c r="C523" s="5" t="s">
         <v>4089</v>
-      </c>
-      <c r="C523" s="5" t="s">
-        <v>4090</v>
       </c>
       <c r="D523" s="5" t="s">
         <v>2586</v>
@@ -32867,13 +32864,13 @@
     </row>
     <row r="525">
       <c r="A525" s="5" t="s">
+        <v>4090</v>
+      </c>
+      <c r="B525" s="5" t="s">
         <v>4091</v>
       </c>
-      <c r="B525" s="5" t="s">
+      <c r="C525" s="5" t="s">
         <v>4092</v>
-      </c>
-      <c r="C525" s="5" t="s">
-        <v>4093</v>
       </c>
       <c r="D525" s="5" t="s">
         <v>2586</v>
@@ -32881,13 +32878,13 @@
     </row>
     <row r="526">
       <c r="A526" s="5" t="s">
+        <v>4093</v>
+      </c>
+      <c r="B526" s="5" t="s">
         <v>4094</v>
       </c>
-      <c r="B526" s="5" t="s">
+      <c r="C526" s="5" t="s">
         <v>4095</v>
-      </c>
-      <c r="C526" s="5" t="s">
-        <v>4096</v>
       </c>
       <c r="D526" s="5" t="s">
         <v>2586</v>
@@ -32895,13 +32892,13 @@
     </row>
     <row r="527">
       <c r="A527" s="5" t="s">
+        <v>4096</v>
+      </c>
+      <c r="B527" s="5" t="s">
         <v>4097</v>
       </c>
-      <c r="B527" s="5" t="s">
+      <c r="C527" s="5" t="s">
         <v>4098</v>
-      </c>
-      <c r="C527" s="5" t="s">
-        <v>4099</v>
       </c>
       <c r="D527" s="5" t="s">
         <v>2586</v>
@@ -32909,13 +32906,13 @@
     </row>
     <row r="528">
       <c r="A528" s="5" t="s">
+        <v>4099</v>
+      </c>
+      <c r="B528" s="5" t="s">
         <v>4100</v>
       </c>
-      <c r="B528" s="5" t="s">
+      <c r="C528" s="5" t="s">
         <v>4101</v>
-      </c>
-      <c r="C528" s="5" t="s">
-        <v>4102</v>
       </c>
       <c r="D528" s="5" t="s">
         <v>2586</v>
@@ -32923,13 +32920,13 @@
     </row>
     <row r="529">
       <c r="A529" s="5" t="s">
+        <v>4102</v>
+      </c>
+      <c r="B529" s="5" t="s">
         <v>4103</v>
       </c>
-      <c r="B529" s="5" t="s">
+      <c r="C529" s="5" t="s">
         <v>4104</v>
-      </c>
-      <c r="C529" s="5" t="s">
-        <v>4105</v>
       </c>
       <c r="D529" s="5" t="s">
         <v>2586</v>
@@ -32937,13 +32934,13 @@
     </row>
     <row r="530">
       <c r="A530" s="5" t="s">
+        <v>4105</v>
+      </c>
+      <c r="B530" s="5" t="s">
         <v>4106</v>
       </c>
-      <c r="B530" s="5" t="s">
+      <c r="C530" s="5" t="s">
         <v>4107</v>
-      </c>
-      <c r="C530" s="5" t="s">
-        <v>4108</v>
       </c>
       <c r="D530" s="5" t="s">
         <v>2586</v>
@@ -32951,13 +32948,13 @@
     </row>
     <row r="531">
       <c r="A531" s="5" t="s">
+        <v>4108</v>
+      </c>
+      <c r="B531" s="5" t="s">
         <v>4109</v>
       </c>
-      <c r="B531" s="5" t="s">
+      <c r="C531" s="5" t="s">
         <v>4110</v>
-      </c>
-      <c r="C531" s="5" t="s">
-        <v>4111</v>
       </c>
       <c r="D531" s="5" t="s">
         <v>2586</v>
@@ -32965,7 +32962,7 @@
     </row>
     <row r="532">
       <c r="A532" s="5" t="s">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="B532" s="5" t="s">
         <v>2606</v>
@@ -32993,13 +32990,13 @@
     </row>
     <row r="534">
       <c r="A534" s="5" t="s">
+        <v>4112</v>
+      </c>
+      <c r="B534" s="5" t="s">
         <v>4113</v>
       </c>
-      <c r="B534" s="5" t="s">
+      <c r="C534" s="5" t="s">
         <v>4114</v>
-      </c>
-      <c r="C534" s="5" t="s">
-        <v>4115</v>
       </c>
       <c r="D534" s="5" t="s">
         <v>2586</v>
@@ -33007,13 +33004,13 @@
     </row>
     <row r="535">
       <c r="A535" s="5" t="s">
+        <v>4115</v>
+      </c>
+      <c r="B535" s="5" t="s">
         <v>4116</v>
       </c>
-      <c r="B535" s="5" t="s">
+      <c r="C535" s="5" t="s">
         <v>4117</v>
-      </c>
-      <c r="C535" s="5" t="s">
-        <v>4118</v>
       </c>
       <c r="D535" s="5" t="s">
         <v>2586</v>
@@ -33021,13 +33018,13 @@
     </row>
     <row r="536">
       <c r="A536" s="5" t="s">
+        <v>4118</v>
+      </c>
+      <c r="B536" s="5" t="s">
         <v>4119</v>
       </c>
-      <c r="B536" s="5" t="s">
+      <c r="C536" s="5" t="s">
         <v>4120</v>
-      </c>
-      <c r="C536" s="5" t="s">
-        <v>4121</v>
       </c>
       <c r="D536" s="5" t="s">
         <v>2586</v>
@@ -33035,7 +33032,7 @@
     </row>
     <row r="537">
       <c r="A537" s="5" t="s">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="B537" s="5" t="s">
         <v>2612</v>
@@ -33049,13 +33046,13 @@
     </row>
     <row r="538">
       <c r="A538" s="5" t="s">
+        <v>4122</v>
+      </c>
+      <c r="B538" s="5" t="s">
         <v>4123</v>
       </c>
-      <c r="B538" s="5" t="s">
+      <c r="C538" s="5" t="s">
         <v>4124</v>
-      </c>
-      <c r="C538" s="5" t="s">
-        <v>4125</v>
       </c>
       <c r="D538" s="5" t="s">
         <v>2586</v>
@@ -33063,13 +33060,13 @@
     </row>
     <row r="539">
       <c r="A539" s="5" t="s">
+        <v>4125</v>
+      </c>
+      <c r="B539" s="5" t="s">
         <v>4126</v>
       </c>
-      <c r="B539" s="5" t="s">
+      <c r="C539" s="5" t="s">
         <v>4127</v>
-      </c>
-      <c r="C539" s="5" t="s">
-        <v>4128</v>
       </c>
       <c r="D539" s="5" t="s">
         <v>2586</v>
@@ -33077,7 +33074,7 @@
     </row>
     <row r="540">
       <c r="A540" s="5" t="s">
-        <v>4129</v>
+        <v>4128</v>
       </c>
       <c r="B540" s="5" t="s">
         <v>2624</v>
@@ -33091,13 +33088,13 @@
     </row>
     <row r="541">
       <c r="A541" s="5" t="s">
+        <v>4129</v>
+      </c>
+      <c r="B541" s="5" t="s">
         <v>4130</v>
       </c>
-      <c r="B541" s="5" t="s">
+      <c r="C541" s="5" t="s">
         <v>4131</v>
-      </c>
-      <c r="C541" s="5" t="s">
-        <v>4132</v>
       </c>
       <c r="D541" s="5" t="s">
         <v>2586</v>
@@ -33105,13 +33102,13 @@
     </row>
     <row r="542">
       <c r="A542" s="5" t="s">
+        <v>4132</v>
+      </c>
+      <c r="B542" s="5" t="s">
         <v>4133</v>
       </c>
-      <c r="B542" s="5" t="s">
+      <c r="C542" s="5" t="s">
         <v>4134</v>
-      </c>
-      <c r="C542" s="5" t="s">
-        <v>4135</v>
       </c>
       <c r="D542" s="5" t="s">
         <v>2586</v>
@@ -33119,13 +33116,13 @@
     </row>
     <row r="543">
       <c r="A543" s="5" t="s">
+        <v>4135</v>
+      </c>
+      <c r="B543" s="5" t="s">
         <v>4136</v>
       </c>
-      <c r="B543" s="5" t="s">
+      <c r="C543" s="5" t="s">
         <v>4137</v>
-      </c>
-      <c r="C543" s="5" t="s">
-        <v>4138</v>
       </c>
       <c r="D543" s="5" t="s">
         <v>2586</v>
@@ -33133,13 +33130,13 @@
     </row>
     <row r="544">
       <c r="A544" s="5" t="s">
+        <v>4138</v>
+      </c>
+      <c r="B544" s="5" t="s">
         <v>4139</v>
       </c>
-      <c r="B544" s="5" t="s">
+      <c r="C544" s="5" t="s">
         <v>4140</v>
-      </c>
-      <c r="C544" s="5" t="s">
-        <v>4141</v>
       </c>
       <c r="D544" s="5" t="s">
         <v>2586</v>
@@ -33147,13 +33144,13 @@
     </row>
     <row r="545">
       <c r="A545" s="5" t="s">
+        <v>4141</v>
+      </c>
+      <c r="B545" s="5" t="s">
         <v>4142</v>
       </c>
-      <c r="B545" s="5" t="s">
+      <c r="C545" s="5" t="s">
         <v>4143</v>
-      </c>
-      <c r="C545" s="5" t="s">
-        <v>4144</v>
       </c>
       <c r="D545" s="5" t="s">
         <v>2586</v>
@@ -33161,13 +33158,13 @@
     </row>
     <row r="546">
       <c r="A546" s="5" t="s">
+        <v>4144</v>
+      </c>
+      <c r="B546" s="5" t="s">
         <v>4145</v>
       </c>
-      <c r="B546" s="5" t="s">
+      <c r="C546" s="5" t="s">
         <v>4146</v>
-      </c>
-      <c r="C546" s="5" t="s">
-        <v>4147</v>
       </c>
       <c r="D546" s="5" t="s">
         <v>2586</v>
@@ -33175,13 +33172,13 @@
     </row>
     <row r="547">
       <c r="A547" s="5" t="s">
+        <v>4147</v>
+      </c>
+      <c r="B547" s="5" t="s">
         <v>4148</v>
       </c>
-      <c r="B547" s="5" t="s">
+      <c r="C547" s="5" t="s">
         <v>4149</v>
-      </c>
-      <c r="C547" s="5" t="s">
-        <v>4150</v>
       </c>
       <c r="D547" s="5" t="s">
         <v>2586</v>
@@ -33189,7 +33186,7 @@
     </row>
     <row r="548">
       <c r="A548" s="5" t="s">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="B548" s="5" t="s">
         <v>2633</v>
@@ -33203,13 +33200,13 @@
     </row>
     <row r="549">
       <c r="A549" s="5" t="s">
+        <v>4151</v>
+      </c>
+      <c r="B549" s="5" t="s">
         <v>4152</v>
       </c>
-      <c r="B549" s="5" t="s">
+      <c r="C549" s="5" t="s">
         <v>4153</v>
-      </c>
-      <c r="C549" s="5" t="s">
-        <v>4154</v>
       </c>
       <c r="D549" s="5" t="s">
         <v>2586</v>
@@ -33217,13 +33214,13 @@
     </row>
     <row r="550">
       <c r="A550" s="5" t="s">
+        <v>4154</v>
+      </c>
+      <c r="B550" s="5" t="s">
         <v>4155</v>
       </c>
-      <c r="B550" s="5" t="s">
+      <c r="C550" s="5" t="s">
         <v>4156</v>
-      </c>
-      <c r="C550" s="5" t="s">
-        <v>4157</v>
       </c>
       <c r="D550" s="5" t="s">
         <v>2586</v>
@@ -33231,7 +33228,7 @@
     </row>
     <row r="551">
       <c r="A551" s="5" t="s">
-        <v>4158</v>
+        <v>4157</v>
       </c>
       <c r="B551" s="5" t="s">
         <v>2639</v>
@@ -33245,13 +33242,13 @@
     </row>
     <row r="552">
       <c r="A552" s="5" t="s">
+        <v>4158</v>
+      </c>
+      <c r="B552" s="5" t="s">
         <v>4159</v>
       </c>
-      <c r="B552" s="5" t="s">
+      <c r="C552" s="5" t="s">
         <v>4160</v>
-      </c>
-      <c r="C552" s="5" t="s">
-        <v>4161</v>
       </c>
       <c r="D552" s="5" t="s">
         <v>2586</v>
@@ -33259,13 +33256,13 @@
     </row>
     <row r="553">
       <c r="A553" s="5" t="s">
+        <v>4161</v>
+      </c>
+      <c r="B553" s="5" t="s">
         <v>4162</v>
       </c>
-      <c r="B553" s="5" t="s">
+      <c r="C553" s="5" t="s">
         <v>4163</v>
-      </c>
-      <c r="C553" s="5" t="s">
-        <v>4164</v>
       </c>
       <c r="D553" s="5" t="s">
         <v>2586</v>
@@ -33273,13 +33270,13 @@
     </row>
     <row r="554">
       <c r="A554" s="5" t="s">
+        <v>4164</v>
+      </c>
+      <c r="B554" s="5" t="s">
         <v>4165</v>
       </c>
-      <c r="B554" s="5" t="s">
+      <c r="C554" s="5" t="s">
         <v>4166</v>
-      </c>
-      <c r="C554" s="5" t="s">
-        <v>4167</v>
       </c>
       <c r="D554" s="5" t="s">
         <v>2586</v>
@@ -33290,7 +33287,7 @@
         <v>2644</v>
       </c>
       <c r="B555" s="5" t="s">
-        <v>4168</v>
+        <v>4167</v>
       </c>
       <c r="C555" s="5" t="s">
         <v>2646</v>
@@ -33301,13 +33298,13 @@
     </row>
     <row r="556">
       <c r="A556" s="5" t="s">
+        <v>4168</v>
+      </c>
+      <c r="B556" s="5" t="s">
         <v>4169</v>
       </c>
-      <c r="B556" s="5" t="s">
+      <c r="C556" s="5" t="s">
         <v>4170</v>
-      </c>
-      <c r="C556" s="5" t="s">
-        <v>4171</v>
       </c>
       <c r="D556" s="5" t="s">
         <v>2586</v>
@@ -33315,13 +33312,13 @@
     </row>
     <row r="557">
       <c r="A557" s="5" t="s">
+        <v>4171</v>
+      </c>
+      <c r="B557" s="5" t="s">
         <v>4172</v>
       </c>
-      <c r="B557" s="5" t="s">
+      <c r="C557" s="5" t="s">
         <v>4173</v>
-      </c>
-      <c r="C557" s="5" t="s">
-        <v>4174</v>
       </c>
       <c r="D557" s="5" t="s">
         <v>2586</v>
@@ -33329,13 +33326,13 @@
     </row>
     <row r="558">
       <c r="A558" s="5" t="s">
+        <v>4174</v>
+      </c>
+      <c r="B558" s="5" t="s">
         <v>4175</v>
       </c>
-      <c r="B558" s="5" t="s">
+      <c r="C558" s="5" t="s">
         <v>4176</v>
-      </c>
-      <c r="C558" s="5" t="s">
-        <v>4177</v>
       </c>
       <c r="D558" s="5" t="s">
         <v>2586</v>
@@ -33343,7 +33340,7 @@
     </row>
     <row r="559">
       <c r="A559" s="5" t="s">
-        <v>4178</v>
+        <v>4177</v>
       </c>
       <c r="B559" s="5" t="s">
         <v>2651</v>
@@ -33371,13 +33368,13 @@
     </row>
     <row r="561">
       <c r="A561" s="5" t="s">
+        <v>4178</v>
+      </c>
+      <c r="B561" s="5" t="s">
         <v>4179</v>
       </c>
-      <c r="B561" s="5" t="s">
+      <c r="C561" s="5" t="s">
         <v>4180</v>
-      </c>
-      <c r="C561" s="5" t="s">
-        <v>4181</v>
       </c>
       <c r="D561" s="5" t="s">
         <v>2586</v>
@@ -33385,13 +33382,13 @@
     </row>
     <row r="562">
       <c r="A562" s="5" t="s">
+        <v>4181</v>
+      </c>
+      <c r="B562" s="5" t="s">
         <v>4182</v>
       </c>
-      <c r="B562" s="5" t="s">
+      <c r="C562" s="5" t="s">
         <v>4183</v>
-      </c>
-      <c r="C562" s="5" t="s">
-        <v>4184</v>
       </c>
       <c r="D562" s="5" t="s">
         <v>2586</v>
@@ -33399,41 +33396,41 @@
     </row>
     <row r="563">
       <c r="A563" s="5" t="s">
+        <v>4184</v>
+      </c>
+      <c r="B563" s="5" t="s">
         <v>4185</v>
       </c>
-      <c r="B563" s="5" t="s">
+      <c r="C563" s="5" t="s">
         <v>4186</v>
       </c>
-      <c r="C563" s="5" t="s">
+      <c r="D563" s="5" t="s">
         <v>4187</v>
-      </c>
-      <c r="D563" s="5" t="s">
-        <v>4188</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="5" t="s">
+        <v>4188</v>
+      </c>
+      <c r="B564" s="5" t="s">
         <v>4189</v>
       </c>
-      <c r="B564" s="5" t="s">
+      <c r="C564" s="5" t="s">
         <v>4190</v>
       </c>
-      <c r="C564" s="5" t="s">
+      <c r="D564" s="5" t="s">
         <v>4191</v>
-      </c>
-      <c r="D564" s="5" t="s">
-        <v>4192</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="5" t="s">
+        <v>4192</v>
+      </c>
+      <c r="B565" s="5" t="s">
         <v>4193</v>
       </c>
-      <c r="B565" s="5" t="s">
+      <c r="C565" s="5" t="s">
         <v>4194</v>
-      </c>
-      <c r="C565" s="5" t="s">
-        <v>4195</v>
       </c>
       <c r="D565" s="5" t="s">
         <v>2731</v>
@@ -33441,13 +33438,13 @@
     </row>
     <row r="566">
       <c r="A566" s="5" t="s">
+        <v>4195</v>
+      </c>
+      <c r="B566" s="5" t="s">
         <v>4196</v>
       </c>
-      <c r="B566" s="5" t="s">
+      <c r="C566" s="5" t="s">
         <v>4197</v>
-      </c>
-      <c r="C566" s="5" t="s">
-        <v>4198</v>
       </c>
       <c r="D566" s="5" t="s">
         <v>2731</v>
@@ -33455,13 +33452,13 @@
     </row>
     <row r="567">
       <c r="A567" s="5" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B567" s="5" t="s">
         <v>4199</v>
       </c>
-      <c r="B567" s="5" t="s">
+      <c r="C567" s="5" t="s">
         <v>4200</v>
-      </c>
-      <c r="C567" s="5" t="s">
-        <v>4201</v>
       </c>
       <c r="D567" s="5" t="s">
         <v>2731</v>
@@ -33469,13 +33466,13 @@
     </row>
     <row r="568">
       <c r="A568" s="5" t="s">
+        <v>4201</v>
+      </c>
+      <c r="B568" s="5" t="s">
         <v>4202</v>
       </c>
-      <c r="B568" s="5" t="s">
+      <c r="C568" s="5" t="s">
         <v>4203</v>
-      </c>
-      <c r="C568" s="5" t="s">
-        <v>4204</v>
       </c>
       <c r="D568" s="5" t="s">
         <v>2731</v>
@@ -33483,7 +33480,7 @@
     </row>
     <row r="569">
       <c r="A569" s="5" t="s">
-        <v>4205</v>
+        <v>4204</v>
       </c>
       <c r="B569" s="5" t="s">
         <v>2733</v>
@@ -33497,7 +33494,7 @@
     </row>
     <row r="570">
       <c r="A570" s="5" t="s">
-        <v>4206</v>
+        <v>4205</v>
       </c>
       <c r="B570" s="5" t="s">
         <v>2736</v>
@@ -33511,13 +33508,13 @@
     </row>
     <row r="571">
       <c r="A571" s="5" t="s">
+        <v>4206</v>
+      </c>
+      <c r="B571" s="5" t="s">
         <v>4207</v>
       </c>
-      <c r="B571" s="5" t="s">
+      <c r="C571" s="5" t="s">
         <v>4208</v>
-      </c>
-      <c r="C571" s="5" t="s">
-        <v>4209</v>
       </c>
       <c r="D571" s="5" t="s">
         <v>2731</v>
@@ -33525,13 +33522,13 @@
     </row>
     <row r="572">
       <c r="A572" s="5" t="s">
+        <v>4209</v>
+      </c>
+      <c r="B572" s="5" t="s">
         <v>4210</v>
       </c>
-      <c r="B572" s="5" t="s">
+      <c r="C572" s="5" t="s">
         <v>4211</v>
-      </c>
-      <c r="C572" s="5" t="s">
-        <v>4212</v>
       </c>
       <c r="D572" s="5" t="s">
         <v>2731</v>
@@ -33567,10 +33564,10 @@
     </row>
     <row r="575">
       <c r="A575" s="5" t="s">
+        <v>4212</v>
+      </c>
+      <c r="B575" s="5" t="s">
         <v>4213</v>
-      </c>
-      <c r="B575" s="5" t="s">
-        <v>4214</v>
       </c>
       <c r="C575" s="5" t="s">
         <v>2756</v>
@@ -33595,69 +33592,69 @@
     </row>
     <row r="577">
       <c r="A577" s="5" t="s">
+        <v>4214</v>
+      </c>
+      <c r="B577" s="5" t="s">
         <v>4215</v>
       </c>
-      <c r="B577" s="5" t="s">
+      <c r="C577" s="5" t="s">
         <v>4216</v>
       </c>
-      <c r="C577" s="5" t="s">
+      <c r="D577" s="5" t="s">
         <v>4217</v>
-      </c>
-      <c r="D577" s="5" t="s">
-        <v>4218</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="5" t="s">
+        <v>4218</v>
+      </c>
+      <c r="B578" s="5" t="s">
         <v>4219</v>
       </c>
-      <c r="B578" s="5" t="s">
+      <c r="C578" s="5" t="s">
         <v>4220</v>
       </c>
-      <c r="C578" s="5" t="s">
-        <v>4221</v>
-      </c>
       <c r="D578" s="5" t="s">
-        <v>4218</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="5" t="s">
+        <v>4221</v>
+      </c>
+      <c r="B579" s="5" t="s">
         <v>4222</v>
       </c>
-      <c r="B579" s="5" t="s">
+      <c r="C579" s="5" t="s">
         <v>4223</v>
       </c>
-      <c r="C579" s="5" t="s">
+      <c r="D579" s="5" t="s">
         <v>4224</v>
-      </c>
-      <c r="D579" s="5" t="s">
-        <v>4225</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="5" t="s">
+        <v>4225</v>
+      </c>
+      <c r="B580" s="5" t="s">
         <v>4226</v>
       </c>
-      <c r="B580" s="5" t="s">
+      <c r="C580" s="5" t="s">
         <v>4227</v>
       </c>
-      <c r="C580" s="5" t="s">
+      <c r="D580" s="5" t="s">
         <v>4228</v>
-      </c>
-      <c r="D580" s="5" t="s">
-        <v>4229</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="5" t="s">
+        <v>4229</v>
+      </c>
+      <c r="B581" s="5" t="s">
         <v>4230</v>
       </c>
-      <c r="B581" s="5" t="s">
+      <c r="C581" s="5" t="s">
         <v>4231</v>
-      </c>
-      <c r="C581" s="5" t="s">
-        <v>4232</v>
       </c>
       <c r="D581" s="5" t="s">
         <v>2794</v>
@@ -33665,13 +33662,13 @@
     </row>
     <row r="582">
       <c r="A582" s="5" t="s">
+        <v>4232</v>
+      </c>
+      <c r="B582" s="5" t="s">
         <v>4233</v>
       </c>
-      <c r="B582" s="5" t="s">
+      <c r="C582" s="5" t="s">
         <v>4234</v>
-      </c>
-      <c r="C582" s="5" t="s">
-        <v>4235</v>
       </c>
       <c r="D582" s="5" t="s">
         <v>2794</v>
@@ -33679,13 +33676,13 @@
     </row>
     <row r="583">
       <c r="A583" s="5" t="s">
+        <v>4235</v>
+      </c>
+      <c r="B583" s="5" t="s">
         <v>4236</v>
       </c>
-      <c r="B583" s="5" t="s">
+      <c r="C583" s="5" t="s">
         <v>4237</v>
-      </c>
-      <c r="C583" s="5" t="s">
-        <v>4238</v>
       </c>
       <c r="D583" s="5" t="s">
         <v>2794</v>
@@ -33693,13 +33690,13 @@
     </row>
     <row r="584">
       <c r="A584" s="5" t="s">
+        <v>4238</v>
+      </c>
+      <c r="B584" s="5" t="s">
         <v>4239</v>
       </c>
-      <c r="B584" s="5" t="s">
+      <c r="C584" s="5" t="s">
         <v>4240</v>
-      </c>
-      <c r="C584" s="5" t="s">
-        <v>4241</v>
       </c>
       <c r="D584" s="5" t="s">
         <v>2794</v>
@@ -33707,13 +33704,13 @@
     </row>
     <row r="585">
       <c r="A585" s="5" t="s">
+        <v>4241</v>
+      </c>
+      <c r="B585" s="5" t="s">
         <v>4242</v>
       </c>
-      <c r="B585" s="5" t="s">
+      <c r="C585" s="5" t="s">
         <v>4243</v>
-      </c>
-      <c r="C585" s="5" t="s">
-        <v>4244</v>
       </c>
       <c r="D585" s="5" t="s">
         <v>2794</v>
@@ -33721,13 +33718,13 @@
     </row>
     <row r="586">
       <c r="A586" s="5" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B586" s="5" t="s">
         <v>4245</v>
       </c>
-      <c r="B586" s="5" t="s">
+      <c r="C586" s="5" t="s">
         <v>4246</v>
-      </c>
-      <c r="C586" s="5" t="s">
-        <v>4247</v>
       </c>
       <c r="D586" s="5" t="s">
         <v>2794</v>
@@ -33735,13 +33732,13 @@
     </row>
     <row r="587">
       <c r="A587" s="5" t="s">
+        <v>4247</v>
+      </c>
+      <c r="B587" s="5" t="s">
         <v>4248</v>
       </c>
-      <c r="B587" s="5" t="s">
+      <c r="C587" s="5" t="s">
         <v>4249</v>
-      </c>
-      <c r="C587" s="5" t="s">
-        <v>4250</v>
       </c>
       <c r="D587" s="5" t="s">
         <v>2794</v>
@@ -33749,27 +33746,27 @@
     </row>
     <row r="588">
       <c r="A588" s="5" t="s">
+        <v>4250</v>
+      </c>
+      <c r="B588" s="5" t="s">
         <v>4251</v>
       </c>
-      <c r="B588" s="5" t="s">
+      <c r="C588" s="5" t="s">
         <v>4252</v>
       </c>
-      <c r="C588" s="5" t="s">
+      <c r="D588" s="5" t="s">
         <v>4253</v>
-      </c>
-      <c r="D588" s="5" t="s">
-        <v>4254</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="5" t="s">
+        <v>4254</v>
+      </c>
+      <c r="B589" s="5" t="s">
         <v>4255</v>
       </c>
-      <c r="B589" s="5" t="s">
+      <c r="C589" s="5" t="s">
         <v>4256</v>
-      </c>
-      <c r="C589" s="5" t="s">
-        <v>4257</v>
       </c>
       <c r="D589" s="5" t="s">
         <v>2816</v>
@@ -33777,27 +33774,27 @@
     </row>
     <row r="590">
       <c r="A590" s="5" t="s">
+        <v>4257</v>
+      </c>
+      <c r="B590" s="5" t="s">
+        <v>4257</v>
+      </c>
+      <c r="C590" s="5" t="s">
         <v>4258</v>
       </c>
-      <c r="B590" s="5" t="s">
-        <v>4258</v>
-      </c>
-      <c r="C590" s="5" t="s">
-        <v>4259</v>
-      </c>
       <c r="D590" s="5" t="s">
-        <v>4258</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="5" t="s">
+        <v>4259</v>
+      </c>
+      <c r="B591" s="5" t="s">
         <v>4260</v>
       </c>
-      <c r="B591" s="5" t="s">
+      <c r="C591" s="5" t="s">
         <v>4261</v>
-      </c>
-      <c r="C591" s="5" t="s">
-        <v>4262</v>
       </c>
       <c r="D591" s="5" t="s">
         <v>2820</v>
@@ -33805,10 +33802,10 @@
     </row>
     <row r="592">
       <c r="A592" s="5" t="s">
+        <v>4262</v>
+      </c>
+      <c r="B592" s="5" t="s">
         <v>4263</v>
-      </c>
-      <c r="B592" s="5" t="s">
-        <v>4264</v>
       </c>
       <c r="C592" s="5" t="s">
         <v>2819</v>
